--- a/internal examples/History Query on Embankment/Results/Excess Pore Pressure History (Manual).xlsx
+++ b/internal examples/History Query on Embankment/Results/Excess Pore Pressure History (Manual).xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rocscienceinc-my.sharepoint.com/personal/daniel_wai_rocscience_com/Documents/Rocscience/RS2/Scripting/Examples/history_query_example/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanielWai\source\repos\rs2_python_client_library\internal examples\History Query on Embankment\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{7DA85E26-CD76-4DCC-97B5-D1AA6FD442FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{791E284E-4A16-45CF-8B70-7A1202BB1519}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC46599-BBE4-4087-A683-D12C8AB7A735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB2DA7A1-7DF2-4F08-A18D-FD6136017F0B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB2DA7A1-7DF2-4F08-A18D-FD6136017F0B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="4" r:id="rId1"/>
+    <sheet name="Raw Data" sheetId="4" r:id="rId1"/>
     <sheet name="Chart" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="47">
   <si>
     <t>History Query Pore Pressure</t>
   </si>
@@ -77,12 +77,114 @@
   <si>
     <t xml:space="preserve"> Pore Pressure [kPa]</t>
   </si>
+  <si>
+    <t>HQ 2 Stage 2</t>
+  </si>
+  <si>
+    <t>HQ 2 Stage 3</t>
+  </si>
+  <si>
+    <t>HQ 2 Stage 4</t>
+  </si>
+  <si>
+    <t>HQ 2 Stage 5</t>
+  </si>
+  <si>
+    <t>HQ 2 Stage 6</t>
+  </si>
+  <si>
+    <t>HQ 2 Stage 7</t>
+  </si>
+  <si>
+    <t>HQ 2 Stage 8</t>
+  </si>
+  <si>
+    <t>HQ 3 Stage 2</t>
+  </si>
+  <si>
+    <t>HQ 3 Stage 3</t>
+  </si>
+  <si>
+    <t>HQ 3 Stage 4</t>
+  </si>
+  <si>
+    <t>HQ 3 Stage 5</t>
+  </si>
+  <si>
+    <t>HQ 3 Stage 6</t>
+  </si>
+  <si>
+    <t>HQ 3 Stage 7</t>
+  </si>
+  <si>
+    <t>HQ 3 Stage 8</t>
+  </si>
+  <si>
+    <t>HQ 4 Stage 2</t>
+  </si>
+  <si>
+    <t>HQ 4 Stage 3</t>
+  </si>
+  <si>
+    <t>HQ 4 Stage 4</t>
+  </si>
+  <si>
+    <t>HQ 4 Stage 5</t>
+  </si>
+  <si>
+    <t>HQ 4 Stage 6</t>
+  </si>
+  <si>
+    <t>HQ 4 Stage 7</t>
+  </si>
+  <si>
+    <t>HQ 4 Stage 8</t>
+  </si>
+  <si>
+    <t>HQ 5 Stage 2</t>
+  </si>
+  <si>
+    <t>HQ 5 Stage 3</t>
+  </si>
+  <si>
+    <t>HQ 5 Stage 4</t>
+  </si>
+  <si>
+    <t>HQ 5 Stage 5</t>
+  </si>
+  <si>
+    <t>HQ 5 Stage 6</t>
+  </si>
+  <si>
+    <t>HQ 5 Stage 7</t>
+  </si>
+  <si>
+    <t>HQ 5 Stage 8</t>
+  </si>
+  <si>
+    <t>Processed Data</t>
+  </si>
+  <si>
+    <t>HQ 1</t>
+  </si>
+  <si>
+    <t>HQ 2</t>
+  </si>
+  <si>
+    <t>HQ 3</t>
+  </si>
+  <si>
+    <t>HQ 4</t>
+  </si>
+  <si>
+    <t>HQ 5</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,6 +196,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -119,10 +227,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -220,11 +329,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Data!$A$3</c:f>
+              <c:f>'Raw Data'!$AG$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>HQ 1 Stage 2</c:v>
+                  <c:v>HQ 1</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -255,10 +364,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Data!$C$5:$C$8</c:f>
+              <c:f>'Raw Data'!$AF$5:$AF$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -270,27 +379,207 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.01932</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.0386499999999996</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.0386500000000005</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12.019299999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>14.038600000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17.372</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>22.019300000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>24.038599999999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>31.372199999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>38.7057</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46.039200000000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>59.372500000000002</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>60.333300000000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>60.666699999999999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>61.333300000000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>61.666699999999999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Data!$E$5:$E$8</c:f>
+              <c:f>'Raw Data'!$AG$5:$AG$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26.427810000000001</c:v>
+                  <c:v>12.920700000000004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20.114153000000002</c:v>
+                  <c:v>12.577700000000004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15.779340000000001</c:v>
+                  <c:v>10.885300000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10.885300000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11.678100000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.0167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.0571000000000055</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.1283999999999992</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.1283999999999992</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.4708000000000006</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.580600000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.5564000000000036</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.8045000000000044</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.8045000000000044</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6.9403000000000006</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.6343000000000032</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.0010000000000048</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.1540000000000035</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.79390000000000072</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.4953000000000003</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.48210000000000264</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.48210000000000264</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.47490000000000521</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.46800000000000352</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.46130000000000138</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.46130000000000138</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.45490000000000208</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.44850000000000279</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.44230000000000302</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.44230000000000302</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.42470000000000141</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.40810000000000457</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.39229999999999876</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -298,7 +587,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-783E-42AD-A442-EF61E5A92071}"/>
+              <c16:uniqueId val="{00000000-3BD8-4A25-914A-C0F614BABBD7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -307,11 +596,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Data!$A$10</c:f>
+              <c:f>'Raw Data'!$AH$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>HQ 1 Stage 3</c:v>
+                  <c:v>HQ 2</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -342,48 +631,222 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Data!$C$12:$C$16</c:f>
+              <c:f>'Raw Data'!$AF$5:$AF$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.33333299999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.66666700000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>3.01932</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="6">
                   <c:v>5.0386499999999996</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="7">
                   <c:v>8.0386500000000005</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="8">
                   <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12.019299999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>14.038600000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17.372</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>22.019300000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>24.038599999999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>31.372199999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>38.7057</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46.039200000000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>59.372500000000002</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>60.333300000000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>60.666699999999999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>61.333300000000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>61.666699999999999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Data!$E$12:$E$16</c:f>
+              <c:f>'Raw Data'!$AH$5:$AH$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
-                  <c:v>15.779340000000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15.45025</c:v>
+                  <c:v>19.64228</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.7958000000000016</c:v>
+                  <c:v>16.628399999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.934800000000001</c:v>
+                  <c:v>13.6754</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.7273999999999994</c:v>
+                  <c:v>13.6754</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14.4129</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.2299000000000007</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.6538000000000004</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.5383999999999993</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.5383999999999993</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.4797000000000011</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.5484000000000009</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.0433999999999983</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.1283999999999992</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.1283999999999992</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8.8703000000000003</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.6590999999999987</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.3684000000000012</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.3381000000000007</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.90899999999999892</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.56099999999999994</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.54570000000000007</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.54570000000000007</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.5373999999999981</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.52949999999999875</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.52169999999999916</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.52169999999999916</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.51419999999999888</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.50689999999999813</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.4997000000000007</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.4997000000000007</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.47929999999999851</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.46020000000000039</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.44200000000000017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -391,7 +854,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-783E-42AD-A442-EF61E5A92071}"/>
+              <c16:uniqueId val="{00000001-3BD8-4A25-914A-C0F614BABBD7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -400,11 +863,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Data!$A$18</c:f>
+              <c:f>'Raw Data'!$AI$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>HQ 1 Stage 4</c:v>
+                  <c:v>HQ 3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -435,48 +898,222 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Data!$C$20:$C$24</c:f>
+              <c:f>'Raw Data'!$AF$5:$AF$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.33333299999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.66666700000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.01932</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.0386499999999996</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.0386500000000005</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>12.019299999999999</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="11">
                   <c:v>14.038600000000001</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="12">
                   <c:v>17.372</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="13">
                   <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>22.019300000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>24.038599999999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>31.372199999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>38.7057</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46.039200000000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>59.372500000000002</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>60.333300000000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>60.666699999999999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>61.333300000000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>61.666699999999999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Data!$E$20:$E$24</c:f>
+              <c:f>'Raw Data'!$AI$5:$AI$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>26.427810000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.114153000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15.779340000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15.779340000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15.45025</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.7958000000000016</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.934800000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2.7273999999999994</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="9">
+                  <c:v>2.7273999999999994</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>9.9834900000000015</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="11">
                   <c:v>5.895900000000001</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="12">
                   <c:v>3.2337000000000025</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="13">
                   <c:v>2.2513000000000005</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.2513000000000005</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>9.3966000000000012</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.9755000000000003</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.4878999999999998</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.3917000000000002</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.9375</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.57380000000000209</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.5578000000000003</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.5578000000000003</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.54920000000000258</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.5409000000000006</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.53290000000000148</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.53290000000000148</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.5251000000000019</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.51740000000000208</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.51000000000000156</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.51000000000000156</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.48880000000000123</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.46890000000000143</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.45010000000000261</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -484,7 +1121,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-783E-42AD-A442-EF61E5A92071}"/>
+              <c16:uniqueId val="{00000002-3BD8-4A25-914A-C0F614BABBD7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -493,11 +1130,11 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Data!$A$26</c:f>
+              <c:f>'Raw Data'!$AJ$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>HQ 1 Stage 5</c:v>
+                  <c:v>HQ 4</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -528,66 +1165,222 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Data!$C$28:$C$35</c:f>
+              <c:f>'Raw Data'!$AF$5:$AF$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.33333299999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.66666700000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.01932</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.0386499999999996</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.0386500000000005</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12.019299999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>14.038600000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17.372</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="14">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>22.019300000000001</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="16">
                   <c:v>24.038599999999999</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="17">
                   <c:v>31.372199999999999</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="18">
                   <c:v>38.7057</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="19">
                   <c:v>46.039200000000001</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="20">
                   <c:v>59.372500000000002</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="21">
                   <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>60.333300000000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>60.666699999999999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>61.333300000000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>61.666699999999999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Data!$E$28:$E$35</c:f>
+              <c:f>'Raw Data'!$AJ$5:$AJ$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
-                  <c:v>2.2513000000000005</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.3966000000000012</c:v>
+                  <c:v>28.6492</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.9755000000000003</c:v>
+                  <c:v>20.770200000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.4878999999999998</c:v>
+                  <c:v>15.888770000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.3917000000000002</c:v>
+                  <c:v>15.888770000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.9375</c:v>
+                  <c:v>14.194780000000002</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.57380000000000209</c:v>
+                  <c:v>7.2904</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.5578000000000003</c:v>
+                  <c:v>3.7025100000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.5699500000000004</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.5699500000000004</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.6408500000000004</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.3159700000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.9729400000000004</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.0813500000000005</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.0813500000000005</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.9441500000000005</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.2472100000000008</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.2502600000000008</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.2695800000000013</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.85503000000000107</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.52106999999999992</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.50631000000000093</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.50631000000000093</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.49847000000000108</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.49088000000000065</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.48348999999999975</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.48348999999999975</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.47630000000000017</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.46928000000000125</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.46243000000000123</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.46243000000000123</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.44302000000000064</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.42476000000000091</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.40747</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -595,7 +1388,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-783E-42AD-A442-EF61E5A92071}"/>
+              <c16:uniqueId val="{00000003-3BD8-4A25-914A-C0F614BABBD7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -604,11 +1397,11 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Data!$A$37</c:f>
+              <c:f>'Raw Data'!$AK$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>HQ 1 Stage 6</c:v>
+                  <c:v>HQ 5</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -639,42 +1432,222 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Data!$C$39:$C$42</c:f>
+              <c:f>'Raw Data'!$AF$5:$AF$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.33333299999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.66666700000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.01932</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.0386499999999996</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.0386500000000005</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12.019299999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>14.038600000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17.372</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>22.019300000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>24.038599999999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>31.372199999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>38.7057</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46.039200000000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>59.372500000000002</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>60</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="22">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>60.333300000000001</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="24">
                   <c:v>60.666699999999999</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="25">
                   <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>61.333300000000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>61.666699999999999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Data!$E$39:$E$42</c:f>
+              <c:f>'Raw Data'!$AK$5:$AK$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
-                  <c:v>0.5578000000000003</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.54920000000000258</c:v>
+                  <c:v>22.585399999998856</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.5409000000000006</c:v>
+                  <c:v>16.720599999998857</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.53290000000000148</c:v>
+                  <c:v>12.755899999998858</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12.755899999998858</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10.731799999998858</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.6477199999988574</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.9154199999988575</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.0420999999988574</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.0420999999988574</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.2724599999988575</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.0134699999988577</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.3027599999988575</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.6333699999988576</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.6333699999988576</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.7620199999988575</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.9092599999988575</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.7295799999988575</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.99240699999885762</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.67221299999885753</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.40952699999885755</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.39789999999885756</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.39789999999885756</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.39171899999885756</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.38573899999885758</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.37991199999885761</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.37991199999885761</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.37423299999885756</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.3686919999988576</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.3632749999988576</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.3632749999988576</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.3479299999988576</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.33348899999885756</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.31980899999885759</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -682,187 +1655,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-783E-42AD-A442-EF61E5A92071}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Data!$A$44</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>HQ 1 Stage 7</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Data!$C$46:$C$49</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>61</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>61.333300000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>61.666699999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>62</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Data!$E$46:$E$49</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.53290000000000148</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.5251000000000019</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.51740000000000208</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.51000000000000156</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-783E-42AD-A442-EF61E5A92071}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="6"/>
-          <c:order val="6"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Data!$A$51</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>HQ 1 Stage 8</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="60000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Data!$C$53:$C$56</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>62</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>63</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>65</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Data!$E$53:$E$56</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.51000000000000156</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.48880000000000123</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.46890000000000143</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.45010000000000261</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-783E-42AD-A442-EF61E5A92071}"/>
+              <c16:uniqueId val="{00000004-3BD8-4A25-914A-C0F614BABBD7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -874,11 +1667,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="975704304"/>
-        <c:axId val="975734544"/>
+        <c:axId val="1464027887"/>
+        <c:axId val="1464028367"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="975704304"/>
+        <c:axId val="1464027887"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -995,12 +1788,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="975734544"/>
+        <c:crossAx val="1464028367"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="975734544"/>
+        <c:axId val="1464028367"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1112,7 +1905,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="975704304"/>
+        <c:crossAx val="1464027887"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1124,6 +1917,37 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -1728,23 +2552,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B867F84A-F84C-42BD-AC1C-7DA2C6B51D12}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8293F552-599F-4CF6-B597-8B848D71534C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2084,24 +2908,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CF93094-5F77-444D-B067-ABE164C9839C}">
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:AK56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.140625" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" customWidth="1"/>
+    <col min="15" max="15" width="16.140625" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="G1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -2117,85 +2976,577 @@
       <c r="E4" t="s">
         <v>9</v>
       </c>
+      <c r="G4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" t="s">
+        <v>10</v>
+      </c>
+      <c r="O4" t="s">
+        <v>11</v>
+      </c>
+      <c r="P4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>9</v>
+      </c>
+      <c r="S4" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" t="s">
+        <v>10</v>
+      </c>
+      <c r="U4" t="s">
+        <v>11</v>
+      </c>
+      <c r="V4" t="s">
+        <v>12</v>
+      </c>
+      <c r="W4" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B5">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
+        <v>-39.24</v>
+      </c>
+      <c r="E5">
+        <f>D5-D$5</f>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>45</v>
+      </c>
+      <c r="H5">
+        <v>-9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>-29.43</v>
+      </c>
+      <c r="K5">
+        <f>J5-J$5</f>
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>55</v>
+      </c>
+      <c r="N5">
+        <v>-10</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
         <v>-19.62</v>
       </c>
-      <c r="E5">
-        <f>D5-$D$5</f>
+      <c r="Q5">
+        <f>P5-P$5</f>
         <v>0</v>
       </c>
+      <c r="S5">
+        <v>65</v>
+      </c>
+      <c r="T5">
+        <v>-11</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>-9.81</v>
+      </c>
+      <c r="W5">
+        <f>V5-V$5</f>
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>75</v>
+      </c>
+      <c r="Z5">
+        <v>-12</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="3">
+        <v>1.1424200000000001E-12</v>
+      </c>
+      <c r="AC5">
+        <f>AB5-AB$5</f>
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <f>C5</f>
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <f>E5</f>
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <f>K5</f>
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <f>Q5</f>
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <f>W5</f>
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <f>AC5</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B6">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C6">
         <v>0.33333299999999999</v>
       </c>
       <c r="D6">
+        <v>-26.319299999999998</v>
+      </c>
+      <c r="E6">
+        <f t="shared" ref="E6:E8" si="0">D6-D$5</f>
+        <v>12.920700000000004</v>
+      </c>
+      <c r="G6">
+        <v>45</v>
+      </c>
+      <c r="H6">
+        <v>-9</v>
+      </c>
+      <c r="I6">
+        <v>0.33333299999999999</v>
+      </c>
+      <c r="J6">
+        <v>-9.7877200000000002</v>
+      </c>
+      <c r="K6">
+        <f t="shared" ref="K6:K8" si="1">J6-J$5</f>
+        <v>19.64228</v>
+      </c>
+      <c r="M6">
+        <v>55</v>
+      </c>
+      <c r="N6">
+        <v>-10</v>
+      </c>
+      <c r="O6">
+        <v>0.33333299999999999</v>
+      </c>
+      <c r="P6">
         <v>6.8078099999999999</v>
       </c>
-      <c r="E6">
-        <f>D6-$D$5</f>
+      <c r="Q6">
+        <f t="shared" ref="Q6:Q8" si="2">P6-P$5</f>
         <v>26.427810000000001</v>
       </c>
+      <c r="S6">
+        <v>65</v>
+      </c>
+      <c r="T6">
+        <v>-11</v>
+      </c>
+      <c r="U6">
+        <v>0.33333299999999999</v>
+      </c>
+      <c r="V6">
+        <v>18.839200000000002</v>
+      </c>
+      <c r="W6">
+        <f t="shared" ref="W6:W8" si="3">V6-V$5</f>
+        <v>28.6492</v>
+      </c>
+      <c r="Y6">
+        <v>75</v>
+      </c>
+      <c r="Z6">
+        <v>-12</v>
+      </c>
+      <c r="AA6">
+        <v>0.33333299999999999</v>
+      </c>
+      <c r="AB6">
+        <v>22.5854</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" ref="AC6:AC8" si="4">AB6-AB$5</f>
+        <v>22.585399999998856</v>
+      </c>
+      <c r="AF6">
+        <f t="shared" ref="AF6:AF8" si="5">C6</f>
+        <v>0.33333299999999999</v>
+      </c>
+      <c r="AG6">
+        <f t="shared" ref="AG6:AG8" si="6">E6</f>
+        <v>12.920700000000004</v>
+      </c>
+      <c r="AH6">
+        <f>K6</f>
+        <v>19.64228</v>
+      </c>
+      <c r="AI6">
+        <f>Q6</f>
+        <v>26.427810000000001</v>
+      </c>
+      <c r="AJ6">
+        <f>W6</f>
+        <v>28.6492</v>
+      </c>
+      <c r="AK6">
+        <f>AC6</f>
+        <v>22.585399999998856</v>
+      </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B7">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C7">
         <v>0.66666700000000001</v>
       </c>
       <c r="D7">
+        <v>-26.662299999999998</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>12.577700000000004</v>
+      </c>
+      <c r="G7">
+        <v>45</v>
+      </c>
+      <c r="H7">
+        <v>-9</v>
+      </c>
+      <c r="I7">
+        <v>0.66666700000000001</v>
+      </c>
+      <c r="J7">
+        <v>-12.801600000000001</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="1"/>
+        <v>16.628399999999999</v>
+      </c>
+      <c r="M7">
+        <v>55</v>
+      </c>
+      <c r="N7">
+        <v>-10</v>
+      </c>
+      <c r="O7">
+        <v>0.66666700000000001</v>
+      </c>
+      <c r="P7">
         <v>0.49415300000000001</v>
       </c>
-      <c r="E7">
-        <f>D7-$D$5</f>
+      <c r="Q7">
+        <f t="shared" si="2"/>
         <v>20.114153000000002</v>
       </c>
+      <c r="S7">
+        <v>65</v>
+      </c>
+      <c r="T7">
+        <v>-11</v>
+      </c>
+      <c r="U7">
+        <v>0.66666700000000001</v>
+      </c>
+      <c r="V7">
+        <v>10.9602</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="3"/>
+        <v>20.770200000000003</v>
+      </c>
+      <c r="Y7">
+        <v>75</v>
+      </c>
+      <c r="Z7">
+        <v>-12</v>
+      </c>
+      <c r="AA7">
+        <v>0.66666700000000001</v>
+      </c>
+      <c r="AB7">
+        <v>16.720600000000001</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="4"/>
+        <v>16.720599999998857</v>
+      </c>
+      <c r="AF7">
+        <f t="shared" si="5"/>
+        <v>0.66666700000000001</v>
+      </c>
+      <c r="AG7">
+        <f t="shared" si="6"/>
+        <v>12.577700000000004</v>
+      </c>
+      <c r="AH7">
+        <f>K7</f>
+        <v>16.628399999999999</v>
+      </c>
+      <c r="AI7">
+        <f>Q7</f>
+        <v>20.114153000000002</v>
+      </c>
+      <c r="AJ7">
+        <f>W7</f>
+        <v>20.770200000000003</v>
+      </c>
+      <c r="AK7">
+        <f>AC7</f>
+        <v>16.720599999998857</v>
+      </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B8">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
+        <v>-28.354700000000001</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>10.885300000000001</v>
+      </c>
+      <c r="G8">
+        <v>45</v>
+      </c>
+      <c r="H8">
+        <v>-9</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>-15.7546</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="1"/>
+        <v>13.6754</v>
+      </c>
+      <c r="M8">
+        <v>55</v>
+      </c>
+      <c r="N8">
+        <v>-10</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
         <v>-3.8406600000000002</v>
       </c>
-      <c r="E8">
-        <f>D8-$D$5</f>
+      <c r="Q8">
+        <f t="shared" si="2"/>
         <v>15.779340000000001</v>
       </c>
+      <c r="S8">
+        <v>65</v>
+      </c>
+      <c r="T8">
+        <v>-11</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>6.0787699999999996</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="3"/>
+        <v>15.888770000000001</v>
+      </c>
+      <c r="Y8">
+        <v>75</v>
+      </c>
+      <c r="Z8">
+        <v>-12</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>12.7559</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="4"/>
+        <v>12.755899999998858</v>
+      </c>
+      <c r="AF8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="6"/>
+        <v>10.885300000000001</v>
+      </c>
+      <c r="AH8">
+        <f>K8</f>
+        <v>13.6754</v>
+      </c>
+      <c r="AI8">
+        <f>Q8</f>
+        <v>15.779340000000001</v>
+      </c>
+      <c r="AJ8">
+        <f>W8</f>
+        <v>15.888770000000001</v>
+      </c>
+      <c r="AK8">
+        <f>AC8</f>
+        <v>12.755899999998858</v>
+      </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AF9">
+        <f>C12</f>
+        <v>1</v>
+      </c>
+      <c r="AG9">
+        <f>E12</f>
+        <v>10.885300000000001</v>
+      </c>
+      <c r="AH9">
+        <f>K12</f>
+        <v>13.6754</v>
+      </c>
+      <c r="AI9">
+        <f>Q12</f>
+        <v>15.779340000000001</v>
+      </c>
+      <c r="AJ9">
+        <f>W12</f>
+        <v>15.888770000000001</v>
+      </c>
+      <c r="AK9">
+        <f>AC12</f>
+        <v>12.755899999998858</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" t="s">
+        <v>21</v>
+      </c>
+      <c r="S10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF10">
+        <f t="shared" ref="AF10:AF13" si="7">C13</f>
+        <v>3.01932</v>
+      </c>
+      <c r="AG10">
+        <f t="shared" ref="AG10:AG13" si="8">E13</f>
+        <v>11.678100000000001</v>
+      </c>
+      <c r="AH10">
+        <f>K13</f>
+        <v>14.4129</v>
+      </c>
+      <c r="AI10">
+        <f>Q13</f>
+        <v>15.45025</v>
+      </c>
+      <c r="AJ10">
+        <f>W13</f>
+        <v>14.194780000000002</v>
+      </c>
+      <c r="AK10">
+        <f>AC13</f>
+        <v>10.731799999998858</v>
+      </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -2211,103 +3562,689 @@
       <c r="E11" t="s">
         <v>9</v>
       </c>
+      <c r="G11" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" t="s">
+        <v>9</v>
+      </c>
+      <c r="M11" t="s">
+        <v>1</v>
+      </c>
+      <c r="N11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O11" t="s">
+        <v>11</v>
+      </c>
+      <c r="P11" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>9</v>
+      </c>
+      <c r="S11" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" t="s">
+        <v>10</v>
+      </c>
+      <c r="U11" t="s">
+        <v>11</v>
+      </c>
+      <c r="V11" t="s">
+        <v>12</v>
+      </c>
+      <c r="W11" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF11">
+        <f t="shared" si="7"/>
+        <v>5.0386499999999996</v>
+      </c>
+      <c r="AG11">
+        <f t="shared" si="8"/>
+        <v>6.0167000000000002</v>
+      </c>
+      <c r="AH11">
+        <f>K14</f>
+        <v>7.2299000000000007</v>
+      </c>
+      <c r="AI11">
+        <f>Q14</f>
+        <v>7.7958000000000016</v>
+      </c>
+      <c r="AJ11">
+        <f>W14</f>
+        <v>7.2904</v>
+      </c>
+      <c r="AK11">
+        <f>AC14</f>
+        <v>5.6477199999988574</v>
+      </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B12">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12">
+        <v>-28.354700000000001</v>
+      </c>
+      <c r="E12">
+        <f t="shared" ref="E12:E16" si="9">D12-D$5</f>
+        <v>10.885300000000001</v>
+      </c>
+      <c r="G12">
+        <v>45</v>
+      </c>
+      <c r="H12">
+        <v>-9</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>-15.7546</v>
+      </c>
+      <c r="K12">
+        <f t="shared" ref="K12:K16" si="10">J12-J$5</f>
+        <v>13.6754</v>
+      </c>
+      <c r="M12">
+        <v>55</v>
+      </c>
+      <c r="N12">
+        <v>-10</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
         <v>-3.8406600000000002</v>
       </c>
-      <c r="E12">
-        <f>D12-$D$5</f>
+      <c r="Q12">
+        <f t="shared" ref="Q12:Q16" si="11">P12-P$5</f>
         <v>15.779340000000001</v>
       </c>
+      <c r="S12">
+        <v>65</v>
+      </c>
+      <c r="T12">
+        <v>-11</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
+        <v>6.0787699999999996</v>
+      </c>
+      <c r="W12">
+        <f t="shared" ref="W12:W16" si="12">V12-V$5</f>
+        <v>15.888770000000001</v>
+      </c>
+      <c r="Y12">
+        <v>75</v>
+      </c>
+      <c r="Z12">
+        <v>-12</v>
+      </c>
+      <c r="AA12">
+        <v>1</v>
+      </c>
+      <c r="AB12">
+        <v>12.7559</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" ref="AC12:AC16" si="13">AB12-AB$5</f>
+        <v>12.755899999998858</v>
+      </c>
+      <c r="AF12">
+        <f t="shared" si="7"/>
+        <v>8.0386500000000005</v>
+      </c>
+      <c r="AG12">
+        <f t="shared" si="8"/>
+        <v>3.0571000000000055</v>
+      </c>
+      <c r="AH12">
+        <f>K15</f>
+        <v>3.6538000000000004</v>
+      </c>
+      <c r="AI12">
+        <f>Q15</f>
+        <v>3.934800000000001</v>
+      </c>
+      <c r="AJ12">
+        <f>W15</f>
+        <v>3.7025100000000002</v>
+      </c>
+      <c r="AK12">
+        <f>AC15</f>
+        <v>2.9154199999988575</v>
+      </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B13">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C13">
         <v>3.01932</v>
       </c>
       <c r="D13">
+        <v>-27.561900000000001</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="9"/>
+        <v>11.678100000000001</v>
+      </c>
+      <c r="G13">
+        <v>45</v>
+      </c>
+      <c r="H13">
+        <v>-9</v>
+      </c>
+      <c r="I13">
+        <v>3.01932</v>
+      </c>
+      <c r="J13">
+        <v>-15.017099999999999</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="10"/>
+        <v>14.4129</v>
+      </c>
+      <c r="M13">
+        <v>55</v>
+      </c>
+      <c r="N13">
+        <v>-10</v>
+      </c>
+      <c r="O13">
+        <v>3.01932</v>
+      </c>
+      <c r="P13">
         <v>-4.1697499999999996</v>
       </c>
-      <c r="E13">
-        <f>D13-$D$5</f>
+      <c r="Q13">
+        <f t="shared" si="11"/>
         <v>15.45025</v>
       </c>
+      <c r="S13">
+        <v>65</v>
+      </c>
+      <c r="T13">
+        <v>-11</v>
+      </c>
+      <c r="U13">
+        <v>3.01932</v>
+      </c>
+      <c r="V13">
+        <v>4.3847800000000001</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="12"/>
+        <v>14.194780000000002</v>
+      </c>
+      <c r="Y13">
+        <v>75</v>
+      </c>
+      <c r="Z13">
+        <v>-12</v>
+      </c>
+      <c r="AA13">
+        <v>3.01932</v>
+      </c>
+      <c r="AB13">
+        <v>10.7318</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="13"/>
+        <v>10.731799999998858</v>
+      </c>
+      <c r="AF13">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="AG13">
+        <f t="shared" si="8"/>
+        <v>2.1283999999999992</v>
+      </c>
+      <c r="AH13">
+        <f>K16</f>
+        <v>2.5383999999999993</v>
+      </c>
+      <c r="AI13">
+        <f>Q16</f>
+        <v>2.7273999999999994</v>
+      </c>
+      <c r="AJ13">
+        <f>W16</f>
+        <v>2.5699500000000004</v>
+      </c>
+      <c r="AK13">
+        <f>AC16</f>
+        <v>2.0420999999988574</v>
+      </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B14">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C14">
         <v>5.0386499999999996</v>
       </c>
       <c r="D14">
+        <v>-33.223300000000002</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="9"/>
+        <v>6.0167000000000002</v>
+      </c>
+      <c r="G14">
+        <v>45</v>
+      </c>
+      <c r="H14">
+        <v>-9</v>
+      </c>
+      <c r="I14">
+        <v>5.0386499999999996</v>
+      </c>
+      <c r="J14">
+        <v>-22.200099999999999</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="10"/>
+        <v>7.2299000000000007</v>
+      </c>
+      <c r="M14">
+        <v>55</v>
+      </c>
+      <c r="N14">
+        <v>-10</v>
+      </c>
+      <c r="O14">
+        <v>5.0386499999999996</v>
+      </c>
+      <c r="P14">
         <v>-11.824199999999999</v>
       </c>
-      <c r="E14">
-        <f>D14-$D$5</f>
+      <c r="Q14">
+        <f t="shared" si="11"/>
         <v>7.7958000000000016</v>
       </c>
+      <c r="S14">
+        <v>65</v>
+      </c>
+      <c r="T14">
+        <v>-11</v>
+      </c>
+      <c r="U14">
+        <v>5.0386499999999996</v>
+      </c>
+      <c r="V14">
+        <v>-2.5196000000000001</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="12"/>
+        <v>7.2904</v>
+      </c>
+      <c r="Y14">
+        <v>75</v>
+      </c>
+      <c r="Z14">
+        <v>-12</v>
+      </c>
+      <c r="AA14">
+        <v>5.0386499999999996</v>
+      </c>
+      <c r="AB14">
+        <v>5.6477199999999996</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="13"/>
+        <v>5.6477199999988574</v>
+      </c>
+      <c r="AF14">
+        <f>C20</f>
+        <v>10</v>
+      </c>
+      <c r="AG14">
+        <f>E20</f>
+        <v>2.1283999999999992</v>
+      </c>
+      <c r="AH14">
+        <f>K20</f>
+        <v>2.5383999999999993</v>
+      </c>
+      <c r="AI14">
+        <f>Q20</f>
+        <v>2.7273999999999994</v>
+      </c>
+      <c r="AJ14">
+        <f>W20</f>
+        <v>2.5699500000000004</v>
+      </c>
+      <c r="AK14">
+        <f>AC20</f>
+        <v>2.0420999999988574</v>
+      </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B15">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C15">
         <v>8.0386500000000005</v>
       </c>
       <c r="D15">
+        <v>-36.182899999999997</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="9"/>
+        <v>3.0571000000000055</v>
+      </c>
+      <c r="G15">
+        <v>45</v>
+      </c>
+      <c r="H15">
+        <v>-9</v>
+      </c>
+      <c r="I15">
+        <v>8.0386500000000005</v>
+      </c>
+      <c r="J15">
+        <v>-25.776199999999999</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="10"/>
+        <v>3.6538000000000004</v>
+      </c>
+      <c r="M15">
+        <v>55</v>
+      </c>
+      <c r="N15">
+        <v>-10</v>
+      </c>
+      <c r="O15">
+        <v>8.0386500000000005</v>
+      </c>
+      <c r="P15">
         <v>-15.6852</v>
       </c>
-      <c r="E15">
-        <f>D15-$D$5</f>
+      <c r="Q15">
+        <f t="shared" si="11"/>
         <v>3.934800000000001</v>
       </c>
+      <c r="S15">
+        <v>65</v>
+      </c>
+      <c r="T15">
+        <v>-11</v>
+      </c>
+      <c r="U15">
+        <v>8.0386500000000005</v>
+      </c>
+      <c r="V15">
+        <v>-6.1074900000000003</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="12"/>
+        <v>3.7025100000000002</v>
+      </c>
+      <c r="Y15">
+        <v>75</v>
+      </c>
+      <c r="Z15">
+        <v>-12</v>
+      </c>
+      <c r="AA15">
+        <v>8.0386500000000005</v>
+      </c>
+      <c r="AB15">
+        <v>2.9154200000000001</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="13"/>
+        <v>2.9154199999988575</v>
+      </c>
+      <c r="AF15">
+        <f t="shared" ref="AF15:AF18" si="14">C21</f>
+        <v>12.019299999999999</v>
+      </c>
+      <c r="AG15">
+        <f t="shared" ref="AG15:AG18" si="15">E21</f>
+        <v>7.4708000000000006</v>
+      </c>
+      <c r="AH15">
+        <f>K21</f>
+        <v>9.4797000000000011</v>
+      </c>
+      <c r="AI15">
+        <f>Q21</f>
+        <v>9.9834900000000015</v>
+      </c>
+      <c r="AJ15">
+        <f>W21</f>
+        <v>8.6408500000000004</v>
+      </c>
+      <c r="AK15">
+        <f>AC21</f>
+        <v>6.2724599999988575</v>
+      </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B16">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C16">
         <v>10</v>
       </c>
       <c r="D16">
+        <v>-37.111600000000003</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="9"/>
+        <v>2.1283999999999992</v>
+      </c>
+      <c r="G16">
+        <v>45</v>
+      </c>
+      <c r="H16">
+        <v>-9</v>
+      </c>
+      <c r="I16">
+        <v>10</v>
+      </c>
+      <c r="J16">
+        <v>-26.8916</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="10"/>
+        <v>2.5383999999999993</v>
+      </c>
+      <c r="M16">
+        <v>55</v>
+      </c>
+      <c r="N16">
+        <v>-10</v>
+      </c>
+      <c r="O16">
+        <v>10</v>
+      </c>
+      <c r="P16">
         <v>-16.892600000000002</v>
       </c>
-      <c r="E16">
-        <f>D16-$D$5</f>
+      <c r="Q16">
+        <f t="shared" si="11"/>
         <v>2.7273999999999994</v>
       </c>
+      <c r="S16">
+        <v>65</v>
+      </c>
+      <c r="T16">
+        <v>-11</v>
+      </c>
+      <c r="U16">
+        <v>10</v>
+      </c>
+      <c r="V16">
+        <v>-7.2400500000000001</v>
+      </c>
+      <c r="W16">
+        <f t="shared" si="12"/>
+        <v>2.5699500000000004</v>
+      </c>
+      <c r="Y16">
+        <v>75</v>
+      </c>
+      <c r="Z16">
+        <v>-12</v>
+      </c>
+      <c r="AA16">
+        <v>10</v>
+      </c>
+      <c r="AB16">
+        <v>2.0421</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" si="13"/>
+        <v>2.0420999999988574</v>
+      </c>
+      <c r="AF16">
+        <f t="shared" si="14"/>
+        <v>14.038600000000001</v>
+      </c>
+      <c r="AG16">
+        <f t="shared" si="15"/>
+        <v>4.580600000000004</v>
+      </c>
+      <c r="AH16">
+        <f>K22</f>
+        <v>5.5484000000000009</v>
+      </c>
+      <c r="AI16">
+        <f>Q22</f>
+        <v>5.895900000000001</v>
+      </c>
+      <c r="AJ16">
+        <f>W22</f>
+        <v>5.3159700000000001</v>
+      </c>
+      <c r="AK16">
+        <f>AC22</f>
+        <v>4.0134699999988577</v>
+      </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AF17">
+        <f t="shared" si="14"/>
+        <v>17.372</v>
+      </c>
+      <c r="AG17">
+        <f t="shared" si="15"/>
+        <v>2.5564000000000036</v>
+      </c>
+      <c r="AH17">
+        <f>K23</f>
+        <v>3.0433999999999983</v>
+      </c>
+      <c r="AI17">
+        <f>Q23</f>
+        <v>3.2337000000000025</v>
+      </c>
+      <c r="AJ17">
+        <f>W23</f>
+        <v>2.9729400000000004</v>
+      </c>
+      <c r="AK17">
+        <f>AC23</f>
+        <v>2.3027599999988575</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
+      <c r="G18" t="s">
+        <v>15</v>
+      </c>
+      <c r="M18" t="s">
+        <v>22</v>
+      </c>
+      <c r="S18" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF18">
+        <f t="shared" si="14"/>
+        <v>20</v>
+      </c>
+      <c r="AG18">
+        <f t="shared" si="15"/>
+        <v>1.8045000000000044</v>
+      </c>
+      <c r="AH18">
+        <f>K24</f>
+        <v>2.1283999999999992</v>
+      </c>
+      <c r="AI18">
+        <f>Q24</f>
+        <v>2.2513000000000005</v>
+      </c>
+      <c r="AJ18">
+        <f>W24</f>
+        <v>2.0813500000000005</v>
+      </c>
+      <c r="AK18">
+        <f>AC24</f>
+        <v>1.6333699999988576</v>
+      </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -2323,103 +4260,689 @@
       <c r="E19" t="s">
         <v>9</v>
       </c>
+      <c r="G19" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>10</v>
+      </c>
+      <c r="I19" t="s">
+        <v>11</v>
+      </c>
+      <c r="J19" t="s">
+        <v>12</v>
+      </c>
+      <c r="K19" t="s">
+        <v>9</v>
+      </c>
+      <c r="M19" t="s">
+        <v>1</v>
+      </c>
+      <c r="N19" t="s">
+        <v>10</v>
+      </c>
+      <c r="O19" t="s">
+        <v>11</v>
+      </c>
+      <c r="P19" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>9</v>
+      </c>
+      <c r="S19" t="s">
+        <v>1</v>
+      </c>
+      <c r="T19" t="s">
+        <v>10</v>
+      </c>
+      <c r="U19" t="s">
+        <v>11</v>
+      </c>
+      <c r="V19" t="s">
+        <v>12</v>
+      </c>
+      <c r="W19" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF19">
+        <f>C28</f>
+        <v>20</v>
+      </c>
+      <c r="AG19">
+        <f>E28</f>
+        <v>1.8045000000000044</v>
+      </c>
+      <c r="AH19">
+        <f t="shared" ref="AH19:AH26" si="16">K28</f>
+        <v>2.1283999999999992</v>
+      </c>
+      <c r="AI19">
+        <f t="shared" ref="AI19:AI26" si="17">Q28</f>
+        <v>2.2513000000000005</v>
+      </c>
+      <c r="AJ19">
+        <f t="shared" ref="AJ19:AJ26" si="18">W28</f>
+        <v>2.0813500000000005</v>
+      </c>
+      <c r="AK19">
+        <f t="shared" ref="AK19:AK26" si="19">AC28</f>
+        <v>1.6333699999988576</v>
+      </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B20">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C20">
         <v>10</v>
       </c>
       <c r="D20">
+        <v>-37.111600000000003</v>
+      </c>
+      <c r="E20">
+        <f t="shared" ref="E20:E24" si="20">D20-D$5</f>
+        <v>2.1283999999999992</v>
+      </c>
+      <c r="G20">
+        <v>45</v>
+      </c>
+      <c r="H20">
+        <v>-9</v>
+      </c>
+      <c r="I20">
+        <v>10</v>
+      </c>
+      <c r="J20">
+        <v>-26.8916</v>
+      </c>
+      <c r="K20">
+        <f t="shared" ref="K20:K24" si="21">J20-J$5</f>
+        <v>2.5383999999999993</v>
+      </c>
+      <c r="M20">
+        <v>55</v>
+      </c>
+      <c r="N20">
+        <v>-10</v>
+      </c>
+      <c r="O20">
+        <v>10</v>
+      </c>
+      <c r="P20">
         <v>-16.892600000000002</v>
       </c>
-      <c r="E20">
-        <f>D20-$D$5</f>
+      <c r="Q20">
+        <f t="shared" ref="Q20:Q24" si="22">P20-P$5</f>
         <v>2.7273999999999994</v>
       </c>
+      <c r="S20">
+        <v>65</v>
+      </c>
+      <c r="T20">
+        <v>-11</v>
+      </c>
+      <c r="U20">
+        <v>10</v>
+      </c>
+      <c r="V20">
+        <v>-7.2400500000000001</v>
+      </c>
+      <c r="W20">
+        <f t="shared" ref="W20:W24" si="23">V20-V$5</f>
+        <v>2.5699500000000004</v>
+      </c>
+      <c r="Y20">
+        <v>75</v>
+      </c>
+      <c r="Z20">
+        <v>-12</v>
+      </c>
+      <c r="AA20">
+        <v>10</v>
+      </c>
+      <c r="AB20">
+        <v>2.0421</v>
+      </c>
+      <c r="AC20">
+        <f t="shared" ref="AC20:AC24" si="24">AB20-AB$5</f>
+        <v>2.0420999999988574</v>
+      </c>
+      <c r="AF20">
+        <f t="shared" ref="AF20:AF26" si="25">C29</f>
+        <v>22.019300000000001</v>
+      </c>
+      <c r="AG20">
+        <f t="shared" ref="AG20:AG26" si="26">E29</f>
+        <v>6.9403000000000006</v>
+      </c>
+      <c r="AH20">
+        <f t="shared" si="16"/>
+        <v>8.8703000000000003</v>
+      </c>
+      <c r="AI20">
+        <f t="shared" si="17"/>
+        <v>9.3966000000000012</v>
+      </c>
+      <c r="AJ20">
+        <f t="shared" si="18"/>
+        <v>7.9441500000000005</v>
+      </c>
+      <c r="AK20">
+        <f t="shared" si="19"/>
+        <v>5.7620199999988575</v>
+      </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B21">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C21">
         <v>12.019299999999999</v>
       </c>
       <c r="D21">
+        <v>-31.769200000000001</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="20"/>
+        <v>7.4708000000000006</v>
+      </c>
+      <c r="G21">
+        <v>45</v>
+      </c>
+      <c r="H21">
+        <v>-9</v>
+      </c>
+      <c r="I21">
+        <v>12.019299999999999</v>
+      </c>
+      <c r="J21">
+        <v>-19.950299999999999</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="21"/>
+        <v>9.4797000000000011</v>
+      </c>
+      <c r="M21">
+        <v>55</v>
+      </c>
+      <c r="N21">
+        <v>-10</v>
+      </c>
+      <c r="O21">
+        <v>12.019299999999999</v>
+      </c>
+      <c r="P21">
         <v>-9.6365099999999995</v>
       </c>
-      <c r="E21">
-        <f>D21-$D$5</f>
+      <c r="Q21">
+        <f t="shared" si="22"/>
         <v>9.9834900000000015</v>
       </c>
+      <c r="S21">
+        <v>65</v>
+      </c>
+      <c r="T21">
+        <v>-11</v>
+      </c>
+      <c r="U21">
+        <v>12.019299999999999</v>
+      </c>
+      <c r="V21">
+        <v>-1.1691499999999999</v>
+      </c>
+      <c r="W21">
+        <f t="shared" si="23"/>
+        <v>8.6408500000000004</v>
+      </c>
+      <c r="Y21">
+        <v>75</v>
+      </c>
+      <c r="Z21">
+        <v>-12</v>
+      </c>
+      <c r="AA21">
+        <v>12.019299999999999</v>
+      </c>
+      <c r="AB21">
+        <v>6.2724599999999997</v>
+      </c>
+      <c r="AC21">
+        <f t="shared" si="24"/>
+        <v>6.2724599999988575</v>
+      </c>
+      <c r="AF21">
+        <f t="shared" si="25"/>
+        <v>24.038599999999999</v>
+      </c>
+      <c r="AG21">
+        <f t="shared" si="26"/>
+        <v>4.6343000000000032</v>
+      </c>
+      <c r="AH21">
+        <f t="shared" si="16"/>
+        <v>5.6590999999999987</v>
+      </c>
+      <c r="AI21">
+        <f t="shared" si="17"/>
+        <v>5.9755000000000003</v>
+      </c>
+      <c r="AJ21">
+        <f t="shared" si="18"/>
+        <v>5.2472100000000008</v>
+      </c>
+      <c r="AK21">
+        <f t="shared" si="19"/>
+        <v>3.9092599999988575</v>
+      </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B22">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C22">
         <v>14.038600000000001</v>
       </c>
       <c r="D22">
+        <v>-34.659399999999998</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="20"/>
+        <v>4.580600000000004</v>
+      </c>
+      <c r="G22">
+        <v>45</v>
+      </c>
+      <c r="H22">
+        <v>-9</v>
+      </c>
+      <c r="I22">
+        <v>14.038600000000001</v>
+      </c>
+      <c r="J22">
+        <v>-23.881599999999999</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="21"/>
+        <v>5.5484000000000009</v>
+      </c>
+      <c r="M22">
+        <v>55</v>
+      </c>
+      <c r="N22">
+        <v>-10</v>
+      </c>
+      <c r="O22">
+        <v>14.038600000000001</v>
+      </c>
+      <c r="P22">
         <v>-13.7241</v>
       </c>
-      <c r="E22">
-        <f>D22-$D$5</f>
+      <c r="Q22">
+        <f t="shared" si="22"/>
         <v>5.895900000000001</v>
       </c>
+      <c r="S22">
+        <v>65</v>
+      </c>
+      <c r="T22">
+        <v>-11</v>
+      </c>
+      <c r="U22">
+        <v>14.038600000000001</v>
+      </c>
+      <c r="V22">
+        <v>-4.4940300000000004</v>
+      </c>
+      <c r="W22">
+        <f t="shared" si="23"/>
+        <v>5.3159700000000001</v>
+      </c>
+      <c r="Y22">
+        <v>75</v>
+      </c>
+      <c r="Z22">
+        <v>-12</v>
+      </c>
+      <c r="AA22">
+        <v>14.038600000000001</v>
+      </c>
+      <c r="AB22">
+        <v>4.0134699999999999</v>
+      </c>
+      <c r="AC22">
+        <f t="shared" si="24"/>
+        <v>4.0134699999988577</v>
+      </c>
+      <c r="AF22">
+        <f t="shared" si="25"/>
+        <v>31.372199999999999</v>
+      </c>
+      <c r="AG22">
+        <f t="shared" si="26"/>
+        <v>2.0010000000000048</v>
+      </c>
+      <c r="AH22">
+        <f t="shared" si="16"/>
+        <v>2.3684000000000012</v>
+      </c>
+      <c r="AI22">
+        <f t="shared" si="17"/>
+        <v>2.4878999999999998</v>
+      </c>
+      <c r="AJ22">
+        <f t="shared" si="18"/>
+        <v>2.2502600000000008</v>
+      </c>
+      <c r="AK22">
+        <f t="shared" si="19"/>
+        <v>1.7295799999988575</v>
+      </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B23">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C23">
         <v>17.372</v>
       </c>
       <c r="D23">
+        <v>-36.683599999999998</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="20"/>
+        <v>2.5564000000000036</v>
+      </c>
+      <c r="G23">
+        <v>45</v>
+      </c>
+      <c r="H23">
+        <v>-9</v>
+      </c>
+      <c r="I23">
+        <v>17.372</v>
+      </c>
+      <c r="J23">
+        <v>-26.386600000000001</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="21"/>
+        <v>3.0433999999999983</v>
+      </c>
+      <c r="M23">
+        <v>55</v>
+      </c>
+      <c r="N23">
+        <v>-10</v>
+      </c>
+      <c r="O23">
+        <v>17.372</v>
+      </c>
+      <c r="P23">
         <v>-16.386299999999999</v>
       </c>
-      <c r="E23">
-        <f>D23-$D$5</f>
+      <c r="Q23">
+        <f t="shared" si="22"/>
         <v>3.2337000000000025</v>
       </c>
+      <c r="S23">
+        <v>65</v>
+      </c>
+      <c r="T23">
+        <v>-11</v>
+      </c>
+      <c r="U23">
+        <v>17.372</v>
+      </c>
+      <c r="V23">
+        <v>-6.8370600000000001</v>
+      </c>
+      <c r="W23">
+        <f t="shared" si="23"/>
+        <v>2.9729400000000004</v>
+      </c>
+      <c r="Y23">
+        <v>75</v>
+      </c>
+      <c r="Z23">
+        <v>-12</v>
+      </c>
+      <c r="AA23">
+        <v>17.372</v>
+      </c>
+      <c r="AB23">
+        <v>2.3027600000000001</v>
+      </c>
+      <c r="AC23">
+        <f t="shared" si="24"/>
+        <v>2.3027599999988575</v>
+      </c>
+      <c r="AF23">
+        <f t="shared" si="25"/>
+        <v>38.7057</v>
+      </c>
+      <c r="AG23">
+        <f t="shared" si="26"/>
+        <v>1.1540000000000035</v>
+      </c>
+      <c r="AH23">
+        <f t="shared" si="16"/>
+        <v>1.3381000000000007</v>
+      </c>
+      <c r="AI23">
+        <f t="shared" si="17"/>
+        <v>1.3917000000000002</v>
+      </c>
+      <c r="AJ23">
+        <f t="shared" si="18"/>
+        <v>1.2695800000000013</v>
+      </c>
+      <c r="AK23">
+        <f t="shared" si="19"/>
+        <v>0.99240699999885762</v>
+      </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B24">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C24">
         <v>20</v>
       </c>
       <c r="D24">
+        <v>-37.435499999999998</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="20"/>
+        <v>1.8045000000000044</v>
+      </c>
+      <c r="G24">
+        <v>45</v>
+      </c>
+      <c r="H24">
+        <v>-9</v>
+      </c>
+      <c r="I24">
+        <v>20</v>
+      </c>
+      <c r="J24">
+        <v>-27.301600000000001</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="21"/>
+        <v>2.1283999999999992</v>
+      </c>
+      <c r="M24">
+        <v>55</v>
+      </c>
+      <c r="N24">
+        <v>-10</v>
+      </c>
+      <c r="O24">
+        <v>20</v>
+      </c>
+      <c r="P24">
         <v>-17.3687</v>
       </c>
-      <c r="E24">
-        <f>D24-$D$5</f>
+      <c r="Q24">
+        <f t="shared" si="22"/>
         <v>2.2513000000000005</v>
       </c>
+      <c r="S24">
+        <v>65</v>
+      </c>
+      <c r="T24">
+        <v>-11</v>
+      </c>
+      <c r="U24">
+        <v>20</v>
+      </c>
+      <c r="V24">
+        <v>-7.72865</v>
+      </c>
+      <c r="W24">
+        <f t="shared" si="23"/>
+        <v>2.0813500000000005</v>
+      </c>
+      <c r="Y24">
+        <v>75</v>
+      </c>
+      <c r="Z24">
+        <v>-12</v>
+      </c>
+      <c r="AA24">
+        <v>20</v>
+      </c>
+      <c r="AB24">
+        <v>1.63337</v>
+      </c>
+      <c r="AC24">
+        <f t="shared" si="24"/>
+        <v>1.6333699999988576</v>
+      </c>
+      <c r="AF24">
+        <f t="shared" si="25"/>
+        <v>46.039200000000001</v>
+      </c>
+      <c r="AG24">
+        <f t="shared" si="26"/>
+        <v>0.79390000000000072</v>
+      </c>
+      <c r="AH24">
+        <f t="shared" si="16"/>
+        <v>0.90899999999999892</v>
+      </c>
+      <c r="AI24">
+        <f t="shared" si="17"/>
+        <v>0.9375</v>
+      </c>
+      <c r="AJ24">
+        <f t="shared" si="18"/>
+        <v>0.85503000000000107</v>
+      </c>
+      <c r="AK24">
+        <f t="shared" si="19"/>
+        <v>0.67221299999885753</v>
+      </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AF25">
+        <f t="shared" si="25"/>
+        <v>59.372500000000002</v>
+      </c>
+      <c r="AG25">
+        <f t="shared" si="26"/>
+        <v>0.4953000000000003</v>
+      </c>
+      <c r="AH25">
+        <f t="shared" si="16"/>
+        <v>0.56099999999999994</v>
+      </c>
+      <c r="AI25">
+        <f t="shared" si="17"/>
+        <v>0.57380000000000209</v>
+      </c>
+      <c r="AJ25">
+        <f t="shared" si="18"/>
+        <v>0.52106999999999992</v>
+      </c>
+      <c r="AK25">
+        <f t="shared" si="19"/>
+        <v>0.40952699999885755</v>
+      </c>
+    </row>
+    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>5</v>
       </c>
+      <c r="G26" t="s">
+        <v>16</v>
+      </c>
+      <c r="M26" t="s">
+        <v>23</v>
+      </c>
+      <c r="S26" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF26">
+        <f t="shared" si="25"/>
+        <v>60</v>
+      </c>
+      <c r="AG26">
+        <f t="shared" si="26"/>
+        <v>0.48210000000000264</v>
+      </c>
+      <c r="AH26">
+        <f t="shared" si="16"/>
+        <v>0.54570000000000007</v>
+      </c>
+      <c r="AI26">
+        <f t="shared" si="17"/>
+        <v>0.5578000000000003</v>
+      </c>
+      <c r="AJ26">
+        <f t="shared" si="18"/>
+        <v>0.50631000000000093</v>
+      </c>
+      <c r="AK26">
+        <f t="shared" si="19"/>
+        <v>0.39789999999885756</v>
+      </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>1</v>
       </c>
@@ -2435,157 +4958,1007 @@
       <c r="E27" t="s">
         <v>9</v>
       </c>
+      <c r="G27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" t="s">
+        <v>10</v>
+      </c>
+      <c r="I27" t="s">
+        <v>11</v>
+      </c>
+      <c r="J27" t="s">
+        <v>12</v>
+      </c>
+      <c r="K27" t="s">
+        <v>9</v>
+      </c>
+      <c r="M27" t="s">
+        <v>1</v>
+      </c>
+      <c r="N27" t="s">
+        <v>10</v>
+      </c>
+      <c r="O27" t="s">
+        <v>11</v>
+      </c>
+      <c r="P27" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>9</v>
+      </c>
+      <c r="S27" t="s">
+        <v>1</v>
+      </c>
+      <c r="T27" t="s">
+        <v>10</v>
+      </c>
+      <c r="U27" t="s">
+        <v>11</v>
+      </c>
+      <c r="V27" t="s">
+        <v>12</v>
+      </c>
+      <c r="W27" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF27">
+        <f>C39</f>
+        <v>60</v>
+      </c>
+      <c r="AG27">
+        <f>E39</f>
+        <v>0.48210000000000264</v>
+      </c>
+      <c r="AH27">
+        <f>K39</f>
+        <v>0.54570000000000007</v>
+      </c>
+      <c r="AI27">
+        <f>Q39</f>
+        <v>0.5578000000000003</v>
+      </c>
+      <c r="AJ27">
+        <f>W39</f>
+        <v>0.50631000000000093</v>
+      </c>
+      <c r="AK27">
+        <f>AC39</f>
+        <v>0.39789999999885756</v>
+      </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B28">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C28">
         <v>20</v>
       </c>
       <c r="D28">
+        <v>-37.435499999999998</v>
+      </c>
+      <c r="E28">
+        <f t="shared" ref="E28:E35" si="27">D28-D$5</f>
+        <v>1.8045000000000044</v>
+      </c>
+      <c r="G28">
+        <v>45</v>
+      </c>
+      <c r="H28">
+        <v>-9</v>
+      </c>
+      <c r="I28">
+        <v>20</v>
+      </c>
+      <c r="J28">
+        <v>-27.301600000000001</v>
+      </c>
+      <c r="K28">
+        <f t="shared" ref="K28:K35" si="28">J28-J$5</f>
+        <v>2.1283999999999992</v>
+      </c>
+      <c r="M28">
+        <v>55</v>
+      </c>
+      <c r="N28">
+        <v>-10</v>
+      </c>
+      <c r="O28">
+        <v>20</v>
+      </c>
+      <c r="P28">
         <v>-17.3687</v>
       </c>
-      <c r="E28">
-        <f t="shared" ref="E28:E35" si="0">D28-$D$5</f>
+      <c r="Q28">
+        <f t="shared" ref="Q28:Q35" si="29">P28-P$5</f>
         <v>2.2513000000000005</v>
       </c>
+      <c r="S28">
+        <v>65</v>
+      </c>
+      <c r="T28">
+        <v>-11</v>
+      </c>
+      <c r="U28">
+        <v>20</v>
+      </c>
+      <c r="V28">
+        <v>-7.72865</v>
+      </c>
+      <c r="W28">
+        <f t="shared" ref="W28:W35" si="30">V28-V$5</f>
+        <v>2.0813500000000005</v>
+      </c>
+      <c r="Y28">
+        <v>75</v>
+      </c>
+      <c r="Z28">
+        <v>-12</v>
+      </c>
+      <c r="AA28">
+        <v>20</v>
+      </c>
+      <c r="AB28">
+        <v>1.63337</v>
+      </c>
+      <c r="AC28">
+        <f t="shared" ref="AC28:AC35" si="31">AB28-AB$5</f>
+        <v>1.6333699999988576</v>
+      </c>
+      <c r="AF28">
+        <f t="shared" ref="AF28:AF30" si="32">C40</f>
+        <v>60.333300000000001</v>
+      </c>
+      <c r="AG28">
+        <f t="shared" ref="AG28:AG30" si="33">E40</f>
+        <v>0.47490000000000521</v>
+      </c>
+      <c r="AH28">
+        <f>K40</f>
+        <v>0.5373999999999981</v>
+      </c>
+      <c r="AI28">
+        <f>Q40</f>
+        <v>0.54920000000000258</v>
+      </c>
+      <c r="AJ28">
+        <f>W40</f>
+        <v>0.49847000000000108</v>
+      </c>
+      <c r="AK28">
+        <f>AC40</f>
+        <v>0.39171899999885756</v>
+      </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B29">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C29">
         <v>22.019300000000001</v>
       </c>
       <c r="D29">
+        <v>-32.299700000000001</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="27"/>
+        <v>6.9403000000000006</v>
+      </c>
+      <c r="G29">
+        <v>45</v>
+      </c>
+      <c r="H29">
+        <v>-9</v>
+      </c>
+      <c r="I29">
+        <v>22.019300000000001</v>
+      </c>
+      <c r="J29">
+        <v>-20.559699999999999</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="28"/>
+        <v>8.8703000000000003</v>
+      </c>
+      <c r="M29">
+        <v>55</v>
+      </c>
+      <c r="N29">
+        <v>-10</v>
+      </c>
+      <c r="O29">
+        <v>22.019300000000001</v>
+      </c>
+      <c r="P29">
         <v>-10.2234</v>
       </c>
-      <c r="E29">
-        <f t="shared" si="0"/>
+      <c r="Q29">
+        <f t="shared" si="29"/>
         <v>9.3966000000000012</v>
       </c>
+      <c r="S29">
+        <v>65</v>
+      </c>
+      <c r="T29">
+        <v>-11</v>
+      </c>
+      <c r="U29">
+        <v>22.019300000000001</v>
+      </c>
+      <c r="V29">
+        <v>-1.86585</v>
+      </c>
+      <c r="W29">
+        <f t="shared" si="30"/>
+        <v>7.9441500000000005</v>
+      </c>
+      <c r="Y29">
+        <v>75</v>
+      </c>
+      <c r="Z29">
+        <v>-12</v>
+      </c>
+      <c r="AA29">
+        <v>22.019300000000001</v>
+      </c>
+      <c r="AB29">
+        <v>5.7620199999999997</v>
+      </c>
+      <c r="AC29">
+        <f t="shared" si="31"/>
+        <v>5.7620199999988575</v>
+      </c>
+      <c r="AF29">
+        <f t="shared" si="32"/>
+        <v>60.666699999999999</v>
+      </c>
+      <c r="AG29">
+        <f t="shared" si="33"/>
+        <v>0.46800000000000352</v>
+      </c>
+      <c r="AH29">
+        <f>K41</f>
+        <v>0.52949999999999875</v>
+      </c>
+      <c r="AI29">
+        <f>Q41</f>
+        <v>0.5409000000000006</v>
+      </c>
+      <c r="AJ29">
+        <f>W41</f>
+        <v>0.49088000000000065</v>
+      </c>
+      <c r="AK29">
+        <f>AC41</f>
+        <v>0.38573899999885758</v>
+      </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B30">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C30">
         <v>24.038599999999999</v>
       </c>
       <c r="D30">
+        <v>-34.605699999999999</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="27"/>
+        <v>4.6343000000000032</v>
+      </c>
+      <c r="G30">
+        <v>45</v>
+      </c>
+      <c r="H30">
+        <v>-9</v>
+      </c>
+      <c r="I30">
+        <v>24.038599999999999</v>
+      </c>
+      <c r="J30">
+        <v>-23.770900000000001</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="28"/>
+        <v>5.6590999999999987</v>
+      </c>
+      <c r="M30">
+        <v>55</v>
+      </c>
+      <c r="N30">
+        <v>-10</v>
+      </c>
+      <c r="O30">
+        <v>24.038599999999999</v>
+      </c>
+      <c r="P30">
         <v>-13.644500000000001</v>
       </c>
-      <c r="E30">
-        <f t="shared" si="0"/>
+      <c r="Q30">
+        <f t="shared" si="29"/>
         <v>5.9755000000000003</v>
       </c>
+      <c r="S30">
+        <v>65</v>
+      </c>
+      <c r="T30">
+        <v>-11</v>
+      </c>
+      <c r="U30">
+        <v>24.038599999999999</v>
+      </c>
+      <c r="V30">
+        <v>-4.5627899999999997</v>
+      </c>
+      <c r="W30">
+        <f t="shared" si="30"/>
+        <v>5.2472100000000008</v>
+      </c>
+      <c r="Y30">
+        <v>75</v>
+      </c>
+      <c r="Z30">
+        <v>-12</v>
+      </c>
+      <c r="AA30">
+        <v>24.038599999999999</v>
+      </c>
+      <c r="AB30">
+        <v>3.9092600000000002</v>
+      </c>
+      <c r="AC30">
+        <f t="shared" si="31"/>
+        <v>3.9092599999988575</v>
+      </c>
+      <c r="AF30">
+        <f t="shared" si="32"/>
+        <v>61</v>
+      </c>
+      <c r="AG30">
+        <f t="shared" si="33"/>
+        <v>0.46130000000000138</v>
+      </c>
+      <c r="AH30">
+        <f>K42</f>
+        <v>0.52169999999999916</v>
+      </c>
+      <c r="AI30">
+        <f>Q42</f>
+        <v>0.53290000000000148</v>
+      </c>
+      <c r="AJ30">
+        <f>W42</f>
+        <v>0.48348999999999975</v>
+      </c>
+      <c r="AK30">
+        <f>AC42</f>
+        <v>0.37991199999885761</v>
+      </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B31">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C31">
         <v>31.372199999999999</v>
       </c>
       <c r="D31">
+        <v>-37.238999999999997</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="27"/>
+        <v>2.0010000000000048</v>
+      </c>
+      <c r="G31">
+        <v>45</v>
+      </c>
+      <c r="H31">
+        <v>-9</v>
+      </c>
+      <c r="I31">
+        <v>31.372199999999999</v>
+      </c>
+      <c r="J31">
+        <v>-27.061599999999999</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="28"/>
+        <v>2.3684000000000012</v>
+      </c>
+      <c r="M31">
+        <v>55</v>
+      </c>
+      <c r="N31">
+        <v>-10</v>
+      </c>
+      <c r="O31">
+        <v>31.372199999999999</v>
+      </c>
+      <c r="P31">
         <v>-17.132100000000001</v>
       </c>
-      <c r="E31">
-        <f t="shared" si="0"/>
+      <c r="Q31">
+        <f t="shared" si="29"/>
         <v>2.4878999999999998</v>
       </c>
+      <c r="S31">
+        <v>65</v>
+      </c>
+      <c r="T31">
+        <v>-11</v>
+      </c>
+      <c r="U31">
+        <v>31.372199999999999</v>
+      </c>
+      <c r="V31">
+        <v>-7.5597399999999997</v>
+      </c>
+      <c r="W31">
+        <f t="shared" si="30"/>
+        <v>2.2502600000000008</v>
+      </c>
+      <c r="Y31">
+        <v>75</v>
+      </c>
+      <c r="Z31">
+        <v>-12</v>
+      </c>
+      <c r="AA31">
+        <v>31.372199999999999</v>
+      </c>
+      <c r="AB31">
+        <v>1.7295799999999999</v>
+      </c>
+      <c r="AC31">
+        <f t="shared" si="31"/>
+        <v>1.7295799999988575</v>
+      </c>
+      <c r="AF31">
+        <f>C46</f>
+        <v>61</v>
+      </c>
+      <c r="AG31">
+        <f>E46</f>
+        <v>0.46130000000000138</v>
+      </c>
+      <c r="AH31">
+        <f>K46</f>
+        <v>0.52169999999999916</v>
+      </c>
+      <c r="AI31">
+        <f>Q46</f>
+        <v>0.53290000000000148</v>
+      </c>
+      <c r="AJ31">
+        <f>W46</f>
+        <v>0.48348999999999975</v>
+      </c>
+      <c r="AK31">
+        <f>AC46</f>
+        <v>0.37991199999885761</v>
+      </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B32">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C32">
         <v>38.7057</v>
       </c>
       <c r="D32">
+        <v>-38.085999999999999</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="27"/>
+        <v>1.1540000000000035</v>
+      </c>
+      <c r="G32">
+        <v>45</v>
+      </c>
+      <c r="H32">
+        <v>-9</v>
+      </c>
+      <c r="I32">
+        <v>38.7057</v>
+      </c>
+      <c r="J32">
+        <v>-28.091899999999999</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="28"/>
+        <v>1.3381000000000007</v>
+      </c>
+      <c r="M32">
+        <v>55</v>
+      </c>
+      <c r="N32">
+        <v>-10</v>
+      </c>
+      <c r="O32">
+        <v>38.7057</v>
+      </c>
+      <c r="P32">
         <v>-18.228300000000001</v>
       </c>
-      <c r="E32">
-        <f t="shared" si="0"/>
+      <c r="Q32">
+        <f t="shared" si="29"/>
         <v>1.3917000000000002</v>
       </c>
+      <c r="S32">
+        <v>65</v>
+      </c>
+      <c r="T32">
+        <v>-11</v>
+      </c>
+      <c r="U32">
+        <v>38.7057</v>
+      </c>
+      <c r="V32">
+        <v>-8.5404199999999992</v>
+      </c>
+      <c r="W32">
+        <f t="shared" si="30"/>
+        <v>1.2695800000000013</v>
+      </c>
+      <c r="Y32">
+        <v>75</v>
+      </c>
+      <c r="Z32">
+        <v>-12</v>
+      </c>
+      <c r="AA32">
+        <v>38.7057</v>
+      </c>
+      <c r="AB32">
+        <v>0.99240700000000004</v>
+      </c>
+      <c r="AC32">
+        <f t="shared" si="31"/>
+        <v>0.99240699999885762</v>
+      </c>
+      <c r="AF32">
+        <f t="shared" ref="AF32:AF34" si="34">C47</f>
+        <v>61.333300000000001</v>
+      </c>
+      <c r="AG32">
+        <f t="shared" ref="AG32:AG34" si="35">E47</f>
+        <v>0.45490000000000208</v>
+      </c>
+      <c r="AH32">
+        <f>K47</f>
+        <v>0.51419999999999888</v>
+      </c>
+      <c r="AI32">
+        <f>Q47</f>
+        <v>0.5251000000000019</v>
+      </c>
+      <c r="AJ32">
+        <f>W47</f>
+        <v>0.47630000000000017</v>
+      </c>
+      <c r="AK32">
+        <f>AC47</f>
+        <v>0.37423299999885756</v>
+      </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B33">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C33">
         <v>46.039200000000001</v>
       </c>
       <c r="D33">
+        <v>-38.446100000000001</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="27"/>
+        <v>0.79390000000000072</v>
+      </c>
+      <c r="G33">
+        <v>45</v>
+      </c>
+      <c r="H33">
+        <v>-9</v>
+      </c>
+      <c r="I33">
+        <v>46.039200000000001</v>
+      </c>
+      <c r="J33">
+        <v>-28.521000000000001</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="28"/>
+        <v>0.90899999999999892</v>
+      </c>
+      <c r="M33">
+        <v>55</v>
+      </c>
+      <c r="N33">
+        <v>-10</v>
+      </c>
+      <c r="O33">
+        <v>46.039200000000001</v>
+      </c>
+      <c r="P33">
         <v>-18.682500000000001</v>
       </c>
-      <c r="E33">
-        <f t="shared" si="0"/>
+      <c r="Q33">
+        <f t="shared" si="29"/>
         <v>0.9375</v>
       </c>
+      <c r="S33">
+        <v>65</v>
+      </c>
+      <c r="T33">
+        <v>-11</v>
+      </c>
+      <c r="U33">
+        <v>46.039200000000001</v>
+      </c>
+      <c r="V33">
+        <v>-8.9549699999999994</v>
+      </c>
+      <c r="W33">
+        <f t="shared" si="30"/>
+        <v>0.85503000000000107</v>
+      </c>
+      <c r="Y33">
+        <v>75</v>
+      </c>
+      <c r="Z33">
+        <v>-12</v>
+      </c>
+      <c r="AA33">
+        <v>46.039200000000001</v>
+      </c>
+      <c r="AB33">
+        <v>0.67221299999999995</v>
+      </c>
+      <c r="AC33">
+        <f t="shared" si="31"/>
+        <v>0.67221299999885753</v>
+      </c>
+      <c r="AF33">
+        <f t="shared" si="34"/>
+        <v>61.666699999999999</v>
+      </c>
+      <c r="AG33">
+        <f t="shared" si="35"/>
+        <v>0.44850000000000279</v>
+      </c>
+      <c r="AH33">
+        <f>K48</f>
+        <v>0.50689999999999813</v>
+      </c>
+      <c r="AI33">
+        <f>Q48</f>
+        <v>0.51740000000000208</v>
+      </c>
+      <c r="AJ33">
+        <f>W48</f>
+        <v>0.46928000000000125</v>
+      </c>
+      <c r="AK33">
+        <f>AC48</f>
+        <v>0.3686919999988576</v>
+      </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B34">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C34">
         <v>59.372500000000002</v>
       </c>
       <c r="D34">
+        <v>-38.744700000000002</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="27"/>
+        <v>0.4953000000000003</v>
+      </c>
+      <c r="G34">
+        <v>45</v>
+      </c>
+      <c r="H34">
+        <v>-9</v>
+      </c>
+      <c r="I34">
+        <v>59.372500000000002</v>
+      </c>
+      <c r="J34">
+        <v>-28.869</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="28"/>
+        <v>0.56099999999999994</v>
+      </c>
+      <c r="M34">
+        <v>55</v>
+      </c>
+      <c r="N34">
+        <v>-10</v>
+      </c>
+      <c r="O34">
+        <v>59.372500000000002</v>
+      </c>
+      <c r="P34">
         <v>-19.046199999999999</v>
       </c>
-      <c r="E34">
-        <f t="shared" si="0"/>
+      <c r="Q34">
+        <f t="shared" si="29"/>
         <v>0.57380000000000209</v>
       </c>
+      <c r="S34">
+        <v>65</v>
+      </c>
+      <c r="T34">
+        <v>-11</v>
+      </c>
+      <c r="U34">
+        <v>59.372500000000002</v>
+      </c>
+      <c r="V34">
+        <v>-9.2889300000000006</v>
+      </c>
+      <c r="W34">
+        <f t="shared" si="30"/>
+        <v>0.52106999999999992</v>
+      </c>
+      <c r="Y34">
+        <v>75</v>
+      </c>
+      <c r="Z34">
+        <v>-12</v>
+      </c>
+      <c r="AA34">
+        <v>59.372500000000002</v>
+      </c>
+      <c r="AB34">
+        <v>0.40952699999999997</v>
+      </c>
+      <c r="AC34">
+        <f t="shared" si="31"/>
+        <v>0.40952699999885755</v>
+      </c>
+      <c r="AF34">
+        <f t="shared" si="34"/>
+        <v>62</v>
+      </c>
+      <c r="AG34">
+        <f t="shared" si="35"/>
+        <v>0.44230000000000302</v>
+      </c>
+      <c r="AH34">
+        <f>K49</f>
+        <v>0.4997000000000007</v>
+      </c>
+      <c r="AI34">
+        <f>Q49</f>
+        <v>0.51000000000000156</v>
+      </c>
+      <c r="AJ34">
+        <f>W49</f>
+        <v>0.46243000000000123</v>
+      </c>
+      <c r="AK34">
+        <f>AC49</f>
+        <v>0.3632749999988576</v>
+      </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B35">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C35">
         <v>60</v>
       </c>
       <c r="D35">
+        <v>-38.757899999999999</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="27"/>
+        <v>0.48210000000000264</v>
+      </c>
+      <c r="G35">
+        <v>45</v>
+      </c>
+      <c r="H35">
+        <v>-9</v>
+      </c>
+      <c r="I35">
+        <v>60</v>
+      </c>
+      <c r="J35">
+        <v>-28.8843</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="28"/>
+        <v>0.54570000000000007</v>
+      </c>
+      <c r="M35">
+        <v>55</v>
+      </c>
+      <c r="N35">
+        <v>-10</v>
+      </c>
+      <c r="O35">
+        <v>60</v>
+      </c>
+      <c r="P35">
         <v>-19.062200000000001</v>
       </c>
-      <c r="E35">
-        <f t="shared" si="0"/>
+      <c r="Q35">
+        <f t="shared" si="29"/>
         <v>0.5578000000000003</v>
       </c>
+      <c r="S35">
+        <v>65</v>
+      </c>
+      <c r="T35">
+        <v>-11</v>
+      </c>
+      <c r="U35">
+        <v>60</v>
+      </c>
+      <c r="V35">
+        <v>-9.3036899999999996</v>
+      </c>
+      <c r="W35">
+        <f t="shared" si="30"/>
+        <v>0.50631000000000093</v>
+      </c>
+      <c r="Y35">
+        <v>75</v>
+      </c>
+      <c r="Z35">
+        <v>-12</v>
+      </c>
+      <c r="AA35">
+        <v>60</v>
+      </c>
+      <c r="AB35">
+        <v>0.39789999999999998</v>
+      </c>
+      <c r="AC35">
+        <f t="shared" si="31"/>
+        <v>0.39789999999885756</v>
+      </c>
+      <c r="AF35">
+        <f>C53</f>
+        <v>62</v>
+      </c>
+      <c r="AG35">
+        <f>E53</f>
+        <v>0.44230000000000302</v>
+      </c>
+      <c r="AH35">
+        <f>K53</f>
+        <v>0.4997000000000007</v>
+      </c>
+      <c r="AI35">
+        <f>Q53</f>
+        <v>0.51000000000000156</v>
+      </c>
+      <c r="AJ35">
+        <f>W53</f>
+        <v>0.46243000000000123</v>
+      </c>
+      <c r="AK35">
+        <f>AC53</f>
+        <v>0.3632749999988576</v>
+      </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AF36">
+        <f t="shared" ref="AF36:AF38" si="36">C54</f>
+        <v>63</v>
+      </c>
+      <c r="AG36">
+        <f t="shared" ref="AG36:AG38" si="37">E54</f>
+        <v>0.42470000000000141</v>
+      </c>
+      <c r="AH36">
+        <f>K54</f>
+        <v>0.47929999999999851</v>
+      </c>
+      <c r="AI36">
+        <f>Q54</f>
+        <v>0.48880000000000123</v>
+      </c>
+      <c r="AJ36">
+        <f>W54</f>
+        <v>0.44302000000000064</v>
+      </c>
+      <c r="AK36">
+        <f>AC54</f>
+        <v>0.3479299999988576</v>
+      </c>
+    </row>
+    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>6</v>
       </c>
+      <c r="G37" t="s">
+        <v>17</v>
+      </c>
+      <c r="M37" t="s">
+        <v>24</v>
+      </c>
+      <c r="S37" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF37">
+        <f t="shared" si="36"/>
+        <v>64</v>
+      </c>
+      <c r="AG37">
+        <f t="shared" si="37"/>
+        <v>0.40810000000000457</v>
+      </c>
+      <c r="AH37">
+        <f>K55</f>
+        <v>0.46020000000000039</v>
+      </c>
+      <c r="AI37">
+        <f>Q55</f>
+        <v>0.46890000000000143</v>
+      </c>
+      <c r="AJ37">
+        <f>W55</f>
+        <v>0.42476000000000091</v>
+      </c>
+      <c r="AK37">
+        <f>AC55</f>
+        <v>0.33348899999885756</v>
+      </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>1</v>
       </c>
@@ -2601,85 +5974,437 @@
       <c r="E38" t="s">
         <v>9</v>
       </c>
+      <c r="G38" t="s">
+        <v>1</v>
+      </c>
+      <c r="H38" t="s">
+        <v>10</v>
+      </c>
+      <c r="I38" t="s">
+        <v>11</v>
+      </c>
+      <c r="J38" t="s">
+        <v>12</v>
+      </c>
+      <c r="K38" t="s">
+        <v>9</v>
+      </c>
+      <c r="M38" t="s">
+        <v>1</v>
+      </c>
+      <c r="N38" t="s">
+        <v>10</v>
+      </c>
+      <c r="O38" t="s">
+        <v>11</v>
+      </c>
+      <c r="P38" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>9</v>
+      </c>
+      <c r="S38" t="s">
+        <v>1</v>
+      </c>
+      <c r="T38" t="s">
+        <v>10</v>
+      </c>
+      <c r="U38" t="s">
+        <v>11</v>
+      </c>
+      <c r="V38" t="s">
+        <v>12</v>
+      </c>
+      <c r="W38" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF38">
+        <f t="shared" si="36"/>
+        <v>65</v>
+      </c>
+      <c r="AG38">
+        <f t="shared" si="37"/>
+        <v>0.39229999999999876</v>
+      </c>
+      <c r="AH38">
+        <f>K56</f>
+        <v>0.44200000000000017</v>
+      </c>
+      <c r="AI38">
+        <f>Q56</f>
+        <v>0.45010000000000261</v>
+      </c>
+      <c r="AJ38">
+        <f>W56</f>
+        <v>0.40747</v>
+      </c>
+      <c r="AK38">
+        <f>AC56</f>
+        <v>0.31980899999885759</v>
+      </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B39">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C39">
         <v>60</v>
       </c>
       <c r="D39">
+        <v>-38.757899999999999</v>
+      </c>
+      <c r="E39">
+        <f t="shared" ref="E39:E42" si="38">D39-D$5</f>
+        <v>0.48210000000000264</v>
+      </c>
+      <c r="G39">
+        <v>45</v>
+      </c>
+      <c r="H39">
+        <v>-9</v>
+      </c>
+      <c r="I39">
+        <v>60</v>
+      </c>
+      <c r="J39">
+        <v>-28.8843</v>
+      </c>
+      <c r="K39">
+        <f t="shared" ref="K39:K42" si="39">J39-J$5</f>
+        <v>0.54570000000000007</v>
+      </c>
+      <c r="M39">
+        <v>55</v>
+      </c>
+      <c r="N39">
+        <v>-10</v>
+      </c>
+      <c r="O39">
+        <v>60</v>
+      </c>
+      <c r="P39">
         <v>-19.062200000000001</v>
       </c>
-      <c r="E39">
-        <f>D39-$D$5</f>
+      <c r="Q39">
+        <f t="shared" ref="Q39:Q42" si="40">P39-P$5</f>
         <v>0.5578000000000003</v>
       </c>
+      <c r="S39">
+        <v>65</v>
+      </c>
+      <c r="T39">
+        <v>-11</v>
+      </c>
+      <c r="U39">
+        <v>60</v>
+      </c>
+      <c r="V39">
+        <v>-9.3036899999999996</v>
+      </c>
+      <c r="W39">
+        <f t="shared" ref="W39:W42" si="41">V39-V$5</f>
+        <v>0.50631000000000093</v>
+      </c>
+      <c r="Y39">
+        <v>75</v>
+      </c>
+      <c r="Z39">
+        <v>-12</v>
+      </c>
+      <c r="AA39">
+        <v>60</v>
+      </c>
+      <c r="AB39">
+        <v>0.39789999999999998</v>
+      </c>
+      <c r="AC39">
+        <f t="shared" ref="AC39:AC42" si="42">AB39-AB$5</f>
+        <v>0.39789999999885756</v>
+      </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B40">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C40">
         <v>60.333300000000001</v>
       </c>
       <c r="D40">
+        <v>-38.765099999999997</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="38"/>
+        <v>0.47490000000000521</v>
+      </c>
+      <c r="G40">
+        <v>45</v>
+      </c>
+      <c r="H40">
+        <v>-9</v>
+      </c>
+      <c r="I40">
+        <v>60.333300000000001</v>
+      </c>
+      <c r="J40">
+        <v>-28.892600000000002</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="39"/>
+        <v>0.5373999999999981</v>
+      </c>
+      <c r="M40">
+        <v>55</v>
+      </c>
+      <c r="N40">
+        <v>-10</v>
+      </c>
+      <c r="O40">
+        <v>60.333300000000001</v>
+      </c>
+      <c r="P40">
         <v>-19.070799999999998</v>
       </c>
-      <c r="E40">
-        <f>D40-$D$5</f>
+      <c r="Q40">
+        <f t="shared" si="40"/>
         <v>0.54920000000000258</v>
       </c>
+      <c r="S40">
+        <v>65</v>
+      </c>
+      <c r="T40">
+        <v>-11</v>
+      </c>
+      <c r="U40">
+        <v>60.333300000000001</v>
+      </c>
+      <c r="V40">
+        <v>-9.3115299999999994</v>
+      </c>
+      <c r="W40">
+        <f t="shared" si="41"/>
+        <v>0.49847000000000108</v>
+      </c>
+      <c r="Y40">
+        <v>75</v>
+      </c>
+      <c r="Z40">
+        <v>-12</v>
+      </c>
+      <c r="AA40">
+        <v>60.333300000000001</v>
+      </c>
+      <c r="AB40">
+        <v>0.39171899999999998</v>
+      </c>
+      <c r="AC40">
+        <f t="shared" si="42"/>
+        <v>0.39171899999885756</v>
+      </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B41">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C41">
         <v>60.666699999999999</v>
       </c>
       <c r="D41">
+        <v>-38.771999999999998</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="38"/>
+        <v>0.46800000000000352</v>
+      </c>
+      <c r="G41">
+        <v>45</v>
+      </c>
+      <c r="H41">
+        <v>-9</v>
+      </c>
+      <c r="I41">
+        <v>60.666699999999999</v>
+      </c>
+      <c r="J41">
+        <v>-28.900500000000001</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="39"/>
+        <v>0.52949999999999875</v>
+      </c>
+      <c r="M41">
+        <v>55</v>
+      </c>
+      <c r="N41">
+        <v>-10</v>
+      </c>
+      <c r="O41">
+        <v>60.666699999999999</v>
+      </c>
+      <c r="P41">
         <v>-19.0791</v>
       </c>
-      <c r="E41">
-        <f>D41-$D$5</f>
+      <c r="Q41">
+        <f t="shared" si="40"/>
         <v>0.5409000000000006</v>
       </c>
+      <c r="S41">
+        <v>65</v>
+      </c>
+      <c r="T41">
+        <v>-11</v>
+      </c>
+      <c r="U41">
+        <v>60.666699999999999</v>
+      </c>
+      <c r="V41">
+        <v>-9.3191199999999998</v>
+      </c>
+      <c r="W41">
+        <f t="shared" si="41"/>
+        <v>0.49088000000000065</v>
+      </c>
+      <c r="Y41">
+        <v>75</v>
+      </c>
+      <c r="Z41">
+        <v>-12</v>
+      </c>
+      <c r="AA41">
+        <v>60.666699999999999</v>
+      </c>
+      <c r="AB41">
+        <v>0.385739</v>
+      </c>
+      <c r="AC41">
+        <f t="shared" si="42"/>
+        <v>0.38573899999885758</v>
+      </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B42">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C42">
         <v>61</v>
       </c>
       <c r="D42">
+        <v>-38.778700000000001</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="38"/>
+        <v>0.46130000000000138</v>
+      </c>
+      <c r="G42">
+        <v>45</v>
+      </c>
+      <c r="H42">
+        <v>-9</v>
+      </c>
+      <c r="I42">
+        <v>61</v>
+      </c>
+      <c r="J42">
+        <v>-28.908300000000001</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="39"/>
+        <v>0.52169999999999916</v>
+      </c>
+      <c r="M42">
+        <v>55</v>
+      </c>
+      <c r="N42">
+        <v>-10</v>
+      </c>
+      <c r="O42">
+        <v>61</v>
+      </c>
+      <c r="P42">
         <v>-19.0871</v>
       </c>
-      <c r="E42">
-        <f>D42-$D$5</f>
+      <c r="Q42">
+        <f t="shared" si="40"/>
         <v>0.53290000000000148</v>
       </c>
+      <c r="S42">
+        <v>65</v>
+      </c>
+      <c r="T42">
+        <v>-11</v>
+      </c>
+      <c r="U42">
+        <v>61</v>
+      </c>
+      <c r="V42">
+        <v>-9.3265100000000007</v>
+      </c>
+      <c r="W42">
+        <f t="shared" si="41"/>
+        <v>0.48348999999999975</v>
+      </c>
+      <c r="Y42">
+        <v>75</v>
+      </c>
+      <c r="Z42">
+        <v>-12</v>
+      </c>
+      <c r="AA42">
+        <v>61</v>
+      </c>
+      <c r="AB42">
+        <v>0.37991200000000003</v>
+      </c>
+      <c r="AC42">
+        <f t="shared" si="42"/>
+        <v>0.37991199999885761</v>
+      </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>7</v>
       </c>
+      <c r="G44" t="s">
+        <v>18</v>
+      </c>
+      <c r="M44" t="s">
+        <v>25</v>
+      </c>
+      <c r="S44" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1</v>
       </c>
@@ -2695,85 +6420,413 @@
       <c r="E45" t="s">
         <v>9</v>
       </c>
+      <c r="G45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H45" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" t="s">
+        <v>11</v>
+      </c>
+      <c r="J45" t="s">
+        <v>12</v>
+      </c>
+      <c r="K45" t="s">
+        <v>9</v>
+      </c>
+      <c r="M45" t="s">
+        <v>1</v>
+      </c>
+      <c r="N45" t="s">
+        <v>10</v>
+      </c>
+      <c r="O45" t="s">
+        <v>11</v>
+      </c>
+      <c r="P45" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>9</v>
+      </c>
+      <c r="S45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T45" t="s">
+        <v>10</v>
+      </c>
+      <c r="U45" t="s">
+        <v>11</v>
+      </c>
+      <c r="V45" t="s">
+        <v>12</v>
+      </c>
+      <c r="W45" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B46">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C46">
         <v>61</v>
       </c>
       <c r="D46">
+        <v>-38.778700000000001</v>
+      </c>
+      <c r="E46">
+        <f t="shared" ref="E46:E49" si="43">D46-D$5</f>
+        <v>0.46130000000000138</v>
+      </c>
+      <c r="G46">
+        <v>45</v>
+      </c>
+      <c r="H46">
+        <v>-9</v>
+      </c>
+      <c r="I46">
+        <v>61</v>
+      </c>
+      <c r="J46">
+        <v>-28.908300000000001</v>
+      </c>
+      <c r="K46">
+        <f t="shared" ref="K46:K49" si="44">J46-J$5</f>
+        <v>0.52169999999999916</v>
+      </c>
+      <c r="M46">
+        <v>55</v>
+      </c>
+      <c r="N46">
+        <v>-10</v>
+      </c>
+      <c r="O46">
+        <v>61</v>
+      </c>
+      <c r="P46">
         <v>-19.0871</v>
       </c>
-      <c r="E46">
-        <f>D46-$D$5</f>
+      <c r="Q46">
+        <f t="shared" ref="Q46:Q49" si="45">P46-P$5</f>
         <v>0.53290000000000148</v>
       </c>
+      <c r="S46">
+        <v>65</v>
+      </c>
+      <c r="T46">
+        <v>-11</v>
+      </c>
+      <c r="U46">
+        <v>61</v>
+      </c>
+      <c r="V46">
+        <v>-9.3265100000000007</v>
+      </c>
+      <c r="W46">
+        <f t="shared" ref="W46:W49" si="46">V46-V$5</f>
+        <v>0.48348999999999975</v>
+      </c>
+      <c r="Y46">
+        <v>75</v>
+      </c>
+      <c r="Z46">
+        <v>-12</v>
+      </c>
+      <c r="AA46">
+        <v>61</v>
+      </c>
+      <c r="AB46">
+        <v>0.37991200000000003</v>
+      </c>
+      <c r="AC46">
+        <f t="shared" ref="AC46:AC49" si="47">AB46-AB$5</f>
+        <v>0.37991199999885761</v>
+      </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B47">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C47">
         <v>61.333300000000001</v>
       </c>
       <c r="D47">
+        <v>-38.7851</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="43"/>
+        <v>0.45490000000000208</v>
+      </c>
+      <c r="G47">
+        <v>45</v>
+      </c>
+      <c r="H47">
+        <v>-9</v>
+      </c>
+      <c r="I47">
+        <v>61.333300000000001</v>
+      </c>
+      <c r="J47">
+        <v>-28.915800000000001</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="44"/>
+        <v>0.51419999999999888</v>
+      </c>
+      <c r="M47">
+        <v>55</v>
+      </c>
+      <c r="N47">
+        <v>-10</v>
+      </c>
+      <c r="O47">
+        <v>61.333300000000001</v>
+      </c>
+      <c r="P47">
         <v>-19.094899999999999</v>
       </c>
-      <c r="E47">
-        <f>D47-$D$5</f>
+      <c r="Q47">
+        <f t="shared" si="45"/>
         <v>0.5251000000000019</v>
       </c>
+      <c r="S47">
+        <v>65</v>
+      </c>
+      <c r="T47">
+        <v>-11</v>
+      </c>
+      <c r="U47">
+        <v>61.333300000000001</v>
+      </c>
+      <c r="V47">
+        <v>-9.3337000000000003</v>
+      </c>
+      <c r="W47">
+        <f t="shared" si="46"/>
+        <v>0.47630000000000017</v>
+      </c>
+      <c r="Y47">
+        <v>75</v>
+      </c>
+      <c r="Z47">
+        <v>-12</v>
+      </c>
+      <c r="AA47">
+        <v>61.333300000000001</v>
+      </c>
+      <c r="AB47">
+        <v>0.37423299999999998</v>
+      </c>
+      <c r="AC47">
+        <f t="shared" si="47"/>
+        <v>0.37423299999885756</v>
+      </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B48">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C48">
         <v>61.666699999999999</v>
       </c>
       <c r="D48">
+        <v>-38.791499999999999</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="43"/>
+        <v>0.44850000000000279</v>
+      </c>
+      <c r="G48">
+        <v>45</v>
+      </c>
+      <c r="H48">
+        <v>-9</v>
+      </c>
+      <c r="I48">
+        <v>61.666699999999999</v>
+      </c>
+      <c r="J48">
+        <v>-28.923100000000002</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="44"/>
+        <v>0.50689999999999813</v>
+      </c>
+      <c r="M48">
+        <v>55</v>
+      </c>
+      <c r="N48">
+        <v>-10</v>
+      </c>
+      <c r="O48">
+        <v>61.666699999999999</v>
+      </c>
+      <c r="P48">
         <v>-19.102599999999999</v>
       </c>
-      <c r="E48">
-        <f>D48-$D$5</f>
+      <c r="Q48">
+        <f t="shared" si="45"/>
         <v>0.51740000000000208</v>
       </c>
+      <c r="S48">
+        <v>65</v>
+      </c>
+      <c r="T48">
+        <v>-11</v>
+      </c>
+      <c r="U48">
+        <v>61.666699999999999</v>
+      </c>
+      <c r="V48">
+        <v>-9.3407199999999992</v>
+      </c>
+      <c r="W48">
+        <f t="shared" si="46"/>
+        <v>0.46928000000000125</v>
+      </c>
+      <c r="Y48">
+        <v>75</v>
+      </c>
+      <c r="Z48">
+        <v>-12</v>
+      </c>
+      <c r="AA48">
+        <v>61.666699999999999</v>
+      </c>
+      <c r="AB48">
+        <v>0.36869200000000002</v>
+      </c>
+      <c r="AC48">
+        <f t="shared" si="47"/>
+        <v>0.3686919999988576</v>
+      </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B49">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C49">
         <v>62</v>
       </c>
       <c r="D49">
+        <v>-38.797699999999999</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="43"/>
+        <v>0.44230000000000302</v>
+      </c>
+      <c r="G49">
+        <v>45</v>
+      </c>
+      <c r="H49">
+        <v>-9</v>
+      </c>
+      <c r="I49">
+        <v>62</v>
+      </c>
+      <c r="J49">
+        <v>-28.930299999999999</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="44"/>
+        <v>0.4997000000000007</v>
+      </c>
+      <c r="M49">
+        <v>55</v>
+      </c>
+      <c r="N49">
+        <v>-10</v>
+      </c>
+      <c r="O49">
+        <v>62</v>
+      </c>
+      <c r="P49">
         <v>-19.11</v>
       </c>
-      <c r="E49">
-        <f>D49-$D$5</f>
+      <c r="Q49">
+        <f t="shared" si="45"/>
         <v>0.51000000000000156</v>
       </c>
+      <c r="S49">
+        <v>65</v>
+      </c>
+      <c r="T49">
+        <v>-11</v>
+      </c>
+      <c r="U49">
+        <v>62</v>
+      </c>
+      <c r="V49">
+        <v>-9.3475699999999993</v>
+      </c>
+      <c r="W49">
+        <f t="shared" si="46"/>
+        <v>0.46243000000000123</v>
+      </c>
+      <c r="Y49">
+        <v>75</v>
+      </c>
+      <c r="Z49">
+        <v>-12</v>
+      </c>
+      <c r="AA49">
+        <v>62</v>
+      </c>
+      <c r="AB49">
+        <v>0.36327500000000001</v>
+      </c>
+      <c r="AC49">
+        <f t="shared" si="47"/>
+        <v>0.3632749999988576</v>
+      </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>8</v>
       </c>
+      <c r="G51" t="s">
+        <v>19</v>
+      </c>
+      <c r="M51" t="s">
+        <v>26</v>
+      </c>
+      <c r="S51" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1</v>
       </c>
@@ -2789,80 +6842,397 @@
       <c r="E52" t="s">
         <v>9</v>
       </c>
+      <c r="G52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H52" t="s">
+        <v>10</v>
+      </c>
+      <c r="I52" t="s">
+        <v>11</v>
+      </c>
+      <c r="J52" t="s">
+        <v>12</v>
+      </c>
+      <c r="K52" t="s">
+        <v>9</v>
+      </c>
+      <c r="M52" t="s">
+        <v>1</v>
+      </c>
+      <c r="N52" t="s">
+        <v>10</v>
+      </c>
+      <c r="O52" t="s">
+        <v>11</v>
+      </c>
+      <c r="P52" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>9</v>
+      </c>
+      <c r="S52" t="s">
+        <v>1</v>
+      </c>
+      <c r="T52" t="s">
+        <v>10</v>
+      </c>
+      <c r="U52" t="s">
+        <v>11</v>
+      </c>
+      <c r="V52" t="s">
+        <v>12</v>
+      </c>
+      <c r="W52" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B53">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C53">
         <v>62</v>
       </c>
       <c r="D53">
+        <v>-38.797699999999999</v>
+      </c>
+      <c r="E53">
+        <f t="shared" ref="E53:E56" si="48">D53-D$5</f>
+        <v>0.44230000000000302</v>
+      </c>
+      <c r="G53">
+        <v>45</v>
+      </c>
+      <c r="H53">
+        <v>-9</v>
+      </c>
+      <c r="I53">
+        <v>62</v>
+      </c>
+      <c r="J53">
+        <v>-28.930299999999999</v>
+      </c>
+      <c r="K53">
+        <f t="shared" ref="K53:K56" si="49">J53-J$5</f>
+        <v>0.4997000000000007</v>
+      </c>
+      <c r="M53">
+        <v>55</v>
+      </c>
+      <c r="N53">
+        <v>-10</v>
+      </c>
+      <c r="O53">
+        <v>62</v>
+      </c>
+      <c r="P53">
         <v>-19.11</v>
       </c>
-      <c r="E53">
-        <f>D53-$D$5</f>
+      <c r="Q53">
+        <f t="shared" ref="Q53:Q56" si="50">P53-P$5</f>
         <v>0.51000000000000156</v>
       </c>
+      <c r="S53">
+        <v>65</v>
+      </c>
+      <c r="T53">
+        <v>-11</v>
+      </c>
+      <c r="U53">
+        <v>62</v>
+      </c>
+      <c r="V53">
+        <v>-9.3475699999999993</v>
+      </c>
+      <c r="W53">
+        <f t="shared" ref="W53:W56" si="51">V53-V$5</f>
+        <v>0.46243000000000123</v>
+      </c>
+      <c r="Y53">
+        <v>75</v>
+      </c>
+      <c r="Z53">
+        <v>-12</v>
+      </c>
+      <c r="AA53">
+        <v>62</v>
+      </c>
+      <c r="AB53">
+        <v>0.36327500000000001</v>
+      </c>
+      <c r="AC53">
+        <f t="shared" ref="AC53:AC56" si="52">AB53-AB$5</f>
+        <v>0.3632749999988576</v>
+      </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B54">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C54">
         <v>63</v>
       </c>
       <c r="D54">
+        <v>-38.815300000000001</v>
+      </c>
+      <c r="E54">
+        <f t="shared" si="48"/>
+        <v>0.42470000000000141</v>
+      </c>
+      <c r="G54">
+        <v>45</v>
+      </c>
+      <c r="H54">
+        <v>-9</v>
+      </c>
+      <c r="I54">
+        <v>63</v>
+      </c>
+      <c r="J54">
+        <v>-28.950700000000001</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="49"/>
+        <v>0.47929999999999851</v>
+      </c>
+      <c r="M54">
+        <v>55</v>
+      </c>
+      <c r="N54">
+        <v>-10</v>
+      </c>
+      <c r="O54">
+        <v>63</v>
+      </c>
+      <c r="P54">
         <v>-19.1312</v>
       </c>
-      <c r="E54">
-        <f>D54-$D$5</f>
+      <c r="Q54">
+        <f t="shared" si="50"/>
         <v>0.48880000000000123</v>
       </c>
+      <c r="S54">
+        <v>65</v>
+      </c>
+      <c r="T54">
+        <v>-11</v>
+      </c>
+      <c r="U54">
+        <v>63</v>
+      </c>
+      <c r="V54">
+        <v>-9.3669799999999999</v>
+      </c>
+      <c r="W54">
+        <f t="shared" si="51"/>
+        <v>0.44302000000000064</v>
+      </c>
+      <c r="Y54">
+        <v>75</v>
+      </c>
+      <c r="Z54">
+        <v>-12</v>
+      </c>
+      <c r="AA54">
+        <v>63</v>
+      </c>
+      <c r="AB54">
+        <v>0.34793000000000002</v>
+      </c>
+      <c r="AC54">
+        <f t="shared" si="52"/>
+        <v>0.3479299999988576</v>
+      </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B55">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C55">
         <v>64</v>
       </c>
       <c r="D55">
+        <v>-38.831899999999997</v>
+      </c>
+      <c r="E55">
+        <f t="shared" si="48"/>
+        <v>0.40810000000000457</v>
+      </c>
+      <c r="G55">
+        <v>45</v>
+      </c>
+      <c r="H55">
+        <v>-9</v>
+      </c>
+      <c r="I55">
+        <v>64</v>
+      </c>
+      <c r="J55">
+        <v>-28.969799999999999</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="49"/>
+        <v>0.46020000000000039</v>
+      </c>
+      <c r="M55">
+        <v>55</v>
+      </c>
+      <c r="N55">
+        <v>-10</v>
+      </c>
+      <c r="O55">
+        <v>64</v>
+      </c>
+      <c r="P55">
         <v>-19.1511</v>
       </c>
-      <c r="E55">
-        <f>D55-$D$5</f>
+      <c r="Q55">
+        <f t="shared" si="50"/>
         <v>0.46890000000000143</v>
       </c>
+      <c r="S55">
+        <v>65</v>
+      </c>
+      <c r="T55">
+        <v>-11</v>
+      </c>
+      <c r="U55">
+        <v>64</v>
+      </c>
+      <c r="V55">
+        <v>-9.3852399999999996</v>
+      </c>
+      <c r="W55">
+        <f t="shared" si="51"/>
+        <v>0.42476000000000091</v>
+      </c>
+      <c r="Y55">
+        <v>75</v>
+      </c>
+      <c r="Z55">
+        <v>-12</v>
+      </c>
+      <c r="AA55">
+        <v>64</v>
+      </c>
+      <c r="AB55">
+        <v>0.33348899999999998</v>
+      </c>
+      <c r="AC55">
+        <f t="shared" si="52"/>
+        <v>0.33348899999885756</v>
+      </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B56">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C56">
         <v>65</v>
       </c>
       <c r="D56">
+        <v>-38.847700000000003</v>
+      </c>
+      <c r="E56">
+        <f t="shared" si="48"/>
+        <v>0.39229999999999876</v>
+      </c>
+      <c r="G56">
+        <v>45</v>
+      </c>
+      <c r="H56">
+        <v>-9</v>
+      </c>
+      <c r="I56">
+        <v>65</v>
+      </c>
+      <c r="J56">
+        <v>-28.988</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="49"/>
+        <v>0.44200000000000017</v>
+      </c>
+      <c r="M56">
+        <v>55</v>
+      </c>
+      <c r="N56">
+        <v>-10</v>
+      </c>
+      <c r="O56">
+        <v>65</v>
+      </c>
+      <c r="P56">
         <v>-19.169899999999998</v>
       </c>
-      <c r="E56">
-        <f>D56-$D$5</f>
+      <c r="Q56">
+        <f t="shared" si="50"/>
         <v>0.45010000000000261</v>
+      </c>
+      <c r="S56">
+        <v>65</v>
+      </c>
+      <c r="T56">
+        <v>-11</v>
+      </c>
+      <c r="U56">
+        <v>65</v>
+      </c>
+      <c r="V56">
+        <v>-9.4025300000000005</v>
+      </c>
+      <c r="W56">
+        <f t="shared" si="51"/>
+        <v>0.40747</v>
+      </c>
+      <c r="Y56">
+        <v>75</v>
+      </c>
+      <c r="Z56">
+        <v>-12</v>
+      </c>
+      <c r="AA56">
+        <v>65</v>
+      </c>
+      <c r="AB56">
+        <v>0.31980900000000001</v>
+      </c>
+      <c r="AC56">
+        <f t="shared" si="52"/>
+        <v>0.31980899999885759</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
